--- a/doc/usctranslations.xlsx
+++ b/doc/usctranslations.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="1226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="1476">
   <si>
     <t>Key</t>
   </si>
@@ -77,6 +77,36 @@
     <t>Idioma</t>
   </si>
   <si>
+    <t>login_english</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>英文</t>
+  </si>
+  <si>
+    <t>Inglês</t>
+  </si>
+  <si>
+    <t>Inglés</t>
+  </si>
+  <si>
+    <t>login_chinese</t>
+  </si>
+  <si>
+    <t>Chinese</t>
+  </si>
+  <si>
+    <t>中文</t>
+  </si>
+  <si>
+    <t>Chinês</t>
+  </si>
+  <si>
+    <t>chino</t>
+  </si>
+  <si>
     <t>login_remember_pwd</t>
   </si>
   <si>
@@ -1244,6 +1274,18 @@
     <t>Hora de finalización</t>
   </si>
   <si>
+    <t>comm_channel</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>通道</t>
+  </si>
+  <si>
+    <t>canal</t>
+  </si>
+  <si>
     <t>comm_channel_name</t>
   </si>
   <si>
@@ -1841,6 +1883,24 @@
     <t>State</t>
   </si>
   <si>
+    <t>conf_dev_main_stream</t>
+  </si>
+  <si>
+    <t>Main stream</t>
+  </si>
+  <si>
+    <t>主码流</t>
+  </si>
+  <si>
+    <t>主碼流</t>
+  </si>
+  <si>
+    <t>Convencional</t>
+  </si>
+  <si>
+    <t>corriente principal</t>
+  </si>
+  <si>
     <t>conf_dev_sub_stream</t>
   </si>
   <si>
@@ -3092,9 +3152,6 @@
     <t>lic_channel</t>
   </si>
   <si>
-    <t>Channel</t>
-  </si>
-  <si>
     <t>通道数</t>
   </si>
   <si>
@@ -3705,6 +3762,699 @@
   </si>
   <si>
     <t>Normas</t>
+  </si>
+  <si>
+    <t>ana_classifier</t>
+  </si>
+  <si>
+    <t>Classifier</t>
+  </si>
+  <si>
+    <t>分类器</t>
+  </si>
+  <si>
+    <t>分類器</t>
+  </si>
+  <si>
+    <t>Classificador</t>
+  </si>
+  <si>
+    <t>Clasificador</t>
+  </si>
+  <si>
+    <t>ana_once_2s</t>
+  </si>
+  <si>
+    <t>Once Every 2 Seconds</t>
+  </si>
+  <si>
+    <t>2秒1次</t>
+  </si>
+  <si>
+    <t>Uma vez a cada 2 segundos</t>
+  </si>
+  <si>
+    <t>Una vez cada 2 segundos</t>
+  </si>
+  <si>
+    <t>ana_once_5s</t>
+  </si>
+  <si>
+    <t>Once Every 5 Seconds</t>
+  </si>
+  <si>
+    <t>5秒1次</t>
+  </si>
+  <si>
+    <t>Uma vez a cada 5 segundos</t>
+  </si>
+  <si>
+    <t>Una vez cada 5 segundos</t>
+  </si>
+  <si>
+    <t>ana_once_10s</t>
+  </si>
+  <si>
+    <t>Once Every 10 Seconds</t>
+  </si>
+  <si>
+    <t>10秒1次</t>
+  </si>
+  <si>
+    <t>Uma vez a cada 10 segundos</t>
+  </si>
+  <si>
+    <t>Una vez cada 10 segundos</t>
+  </si>
+  <si>
+    <t>ana_once_30s</t>
+  </si>
+  <si>
+    <t>Once Every 30 Seconds</t>
+  </si>
+  <si>
+    <t>30秒1次</t>
+  </si>
+  <si>
+    <t>Uma vez a cada 30 segundos</t>
+  </si>
+  <si>
+    <t>Una vez cada 30 segundos</t>
+  </si>
+  <si>
+    <t>ana_once_60s</t>
+  </si>
+  <si>
+    <t>Once Every 60 Seconds</t>
+  </si>
+  <si>
+    <t>60秒1次</t>
+  </si>
+  <si>
+    <t>Uma vez a cada 60 segundos</t>
+  </si>
+  <si>
+    <t>Una vez cada 60 segundos</t>
+  </si>
+  <si>
+    <t>ana_once_120s</t>
+  </si>
+  <si>
+    <t>Once Every 120 Seconds</t>
+  </si>
+  <si>
+    <t>120秒1次</t>
+  </si>
+  <si>
+    <t>Uma vez a cada 120 segundos</t>
+  </si>
+  <si>
+    <t>Una vez cada 120 segundos</t>
+  </si>
+  <si>
+    <t>ana_txt_list</t>
+  </si>
+  <si>
+    <t>Text List</t>
+  </si>
+  <si>
+    <t>文本列表</t>
+  </si>
+  <si>
+    <t>文字清單</t>
+  </si>
+  <si>
+    <t>Lista de texto</t>
+  </si>
+  <si>
+    <t>ana_generate_alarm</t>
+  </si>
+  <si>
+    <t>Generate Alarm</t>
+  </si>
+  <si>
+    <t>生成报警</t>
+  </si>
+  <si>
+    <t>生成報警</t>
+  </si>
+  <si>
+    <t>Gerar alarme</t>
+  </si>
+  <si>
+    <t>Generar alarma</t>
+  </si>
+  <si>
+    <t>ana_alarm_class_index</t>
+  </si>
+  <si>
+    <t>Alarm Class Index</t>
+  </si>
+  <si>
+    <t>报警类别索引</t>
+  </si>
+  <si>
+    <t>報警類別索引</t>
+  </si>
+  <si>
+    <t>Índice de classe de alarme</t>
+  </si>
+  <si>
+    <t>Índice de clase de alarma</t>
+  </si>
+  <si>
+    <t>ana_obj_class_list</t>
+  </si>
+  <si>
+    <t>Object Class List</t>
+  </si>
+  <si>
+    <t>目标对象</t>
+  </si>
+  <si>
+    <t>目標對象</t>
+  </si>
+  <si>
+    <t>Lista de classes de objetos</t>
+  </si>
+  <si>
+    <t>Lista de clases de objetos</t>
+  </si>
+  <si>
+    <t>ana_general</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>常规配置</t>
+  </si>
+  <si>
+    <t>常規配置</t>
+  </si>
+  <si>
+    <t>Em geral</t>
+  </si>
+  <si>
+    <t>ana_face_recognition</t>
+  </si>
+  <si>
+    <t>Face Recognition</t>
+  </si>
+  <si>
+    <t>人脸识别</t>
+  </si>
+  <si>
+    <t>人臉識別</t>
+  </si>
+  <si>
+    <t>Reconhecimento facial</t>
+  </si>
+  <si>
+    <t>Reconocimiento facial</t>
+  </si>
+  <si>
+    <t>ana_face_face</t>
+  </si>
+  <si>
+    <t>Face</t>
+  </si>
+  <si>
+    <t>人脸</t>
+  </si>
+  <si>
+    <t>人臉</t>
+  </si>
+  <si>
+    <t>Cara</t>
+  </si>
+  <si>
+    <t>ana_lpre</t>
+  </si>
+  <si>
+    <t>License Plate Recognition</t>
+  </si>
+  <si>
+    <t>车牌识别</t>
+  </si>
+  <si>
+    <t>車牌識別</t>
+  </si>
+  <si>
+    <t>Reconhecimento da placa</t>
+  </si>
+  <si>
+    <t>Reconocimiento de matrículas</t>
+  </si>
+  <si>
+    <t>ana_license_plate</t>
+  </si>
+  <si>
+    <t>License Plate</t>
+  </si>
+  <si>
+    <t>车牌</t>
+  </si>
+  <si>
+    <t>車牌</t>
+  </si>
+  <si>
+    <t>placa</t>
+  </si>
+  <si>
+    <t>matrículas</t>
+  </si>
+  <si>
+    <t>ana_object</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>对象</t>
+  </si>
+  <si>
+    <t>對象</t>
+  </si>
+  <si>
+    <t>Objeto</t>
+  </si>
+  <si>
+    <t>ana_dwell_time</t>
+  </si>
+  <si>
+    <t>Dwell Time</t>
+  </si>
+  <si>
+    <t>停留时间</t>
+  </si>
+  <si>
+    <t>停留時間</t>
+  </si>
+  <si>
+    <t>Tempo de permanência</t>
+  </si>
+  <si>
+    <t>tiempo de permanencia</t>
+  </si>
+  <si>
+    <t>ana_schedule</t>
+  </si>
+  <si>
+    <t>ana_obj_size</t>
+  </si>
+  <si>
+    <t>Detects The Minimum Object Size</t>
+  </si>
+  <si>
+    <t>检测最小对象大小</t>
+  </si>
+  <si>
+    <t>檢測最小對象大小</t>
+  </si>
+  <si>
+    <t>Detecta o tamanho mínimo do objeto</t>
+  </si>
+  <si>
+    <t>Detecta el tamaño mínimo del objeto.</t>
+  </si>
+  <si>
+    <t>ana_direction</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>方向</t>
+  </si>
+  <si>
+    <t>Direção</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>ana_enable_motion_detection</t>
+  </si>
+  <si>
+    <t>Enable Motion Detection</t>
+  </si>
+  <si>
+    <t>开启移动侦测</t>
+  </si>
+  <si>
+    <t>開啓移動偵測</t>
+  </si>
+  <si>
+    <t>Ativar detecção de movimento</t>
+  </si>
+  <si>
+    <t>Activar detección móvil</t>
+  </si>
+  <si>
+    <t>ana_ground_mode</t>
+  </si>
+  <si>
+    <t>Ground Mode</t>
+  </si>
+  <si>
+    <t>地面模式</t>
+  </si>
+  <si>
+    <t>O modo terra</t>
+  </si>
+  <si>
+    <t>Modo tierra</t>
+  </si>
+  <si>
+    <t>ana_enable_color_detection</t>
+  </si>
+  <si>
+    <t>Enable Color Detection</t>
+  </si>
+  <si>
+    <t>开启颜色检测</t>
+  </si>
+  <si>
+    <t>開啓顏色檢測</t>
+  </si>
+  <si>
+    <t>Ativar detecção de cor</t>
+  </si>
+  <si>
+    <t>Detección de color activada</t>
+  </si>
+  <si>
+    <t>ana_text_search</t>
+  </si>
+  <si>
+    <t>Text search</t>
+  </si>
+  <si>
+    <t>文本搜索</t>
+  </si>
+  <si>
+    <t>Pesquisa por texto</t>
+  </si>
+  <si>
+    <t>Búsqueda por texto</t>
+  </si>
+  <si>
+    <t>ana_person_library</t>
+  </si>
+  <si>
+    <t>Person Library</t>
+  </si>
+  <si>
+    <t>人员库</t>
+  </si>
+  <si>
+    <t>人員庫</t>
+  </si>
+  <si>
+    <t>Biblioteca de pessoas</t>
+  </si>
+  <si>
+    <t>Biblioteca de personal</t>
+  </si>
+  <si>
+    <t>ana_face_library</t>
+  </si>
+  <si>
+    <t>Face Library</t>
+  </si>
+  <si>
+    <t>人脸库</t>
+  </si>
+  <si>
+    <t>人臉庫</t>
+  </si>
+  <si>
+    <t>Galeria de faces</t>
+  </si>
+  <si>
+    <t>Galería de rostros</t>
+  </si>
+  <si>
+    <t>ana_face_library_name</t>
+  </si>
+  <si>
+    <t>Face Library Name</t>
+  </si>
+  <si>
+    <t>人脸库名称</t>
+  </si>
+  <si>
+    <t>人臉庫名稱</t>
+  </si>
+  <si>
+    <t>Nome do banco de dados facial</t>
+  </si>
+  <si>
+    <t>Nombre de la base de datos de rostros</t>
+  </si>
+  <si>
+    <t>ana_recording_always</t>
+  </si>
+  <si>
+    <t>Recording Always</t>
+  </si>
+  <si>
+    <t>持续录像</t>
+  </si>
+  <si>
+    <t>持續錄像</t>
+  </si>
+  <si>
+    <t>Gravando sempre</t>
+  </si>
+  <si>
+    <t>Grabando siempre</t>
+  </si>
+  <si>
+    <t>ana_motion_recording</t>
+  </si>
+  <si>
+    <t>Motion Recording</t>
+  </si>
+  <si>
+    <t>移动侦测录像</t>
+  </si>
+  <si>
+    <t>移動偵測錄像</t>
+  </si>
+  <si>
+    <t>Gravação de movimento</t>
+  </si>
+  <si>
+    <t>Grabación de movimiento</t>
+  </si>
+  <si>
+    <t>ana_object_recording</t>
+  </si>
+  <si>
+    <t>Object Recording</t>
+  </si>
+  <si>
+    <t>物体侦测录像</t>
+  </si>
+  <si>
+    <t>物體偵測錄像</t>
+  </si>
+  <si>
+    <t>Gravação de objeto</t>
+  </si>
+  <si>
+    <t>Grabación de objetos</t>
+  </si>
+  <si>
+    <t>ana_motion_object_recording</t>
+  </si>
+  <si>
+    <t>Motion &amp; Object Recording</t>
+  </si>
+  <si>
+    <t>移动&amp;物体侦测录像</t>
+  </si>
+  <si>
+    <t>移動&amp;物體偵測錄像</t>
+  </si>
+  <si>
+    <t>Gravação de movimentos e objetos</t>
+  </si>
+  <si>
+    <t>Grabación de movimiento y objetos</t>
+  </si>
+  <si>
+    <t>ana_not_recording</t>
+  </si>
+  <si>
+    <t>Not Recording</t>
+  </si>
+  <si>
+    <t>不录像</t>
+  </si>
+  <si>
+    <t>不錄像</t>
+  </si>
+  <si>
+    <t>Não está gravando</t>
+  </si>
+  <si>
+    <t>No grabando</t>
+  </si>
+  <si>
+    <t>ana_copy_to</t>
+  </si>
+  <si>
+    <t>Copy To</t>
+  </si>
+  <si>
+    <t>复制到</t>
+  </si>
+  <si>
+    <t>複製到</t>
+  </si>
+  <si>
+    <t>Copiar para</t>
+  </si>
+  <si>
+    <t>Copiar a</t>
+  </si>
+  <si>
+    <t>ana_check_type</t>
+  </si>
+  <si>
+    <t>Rule type</t>
+  </si>
+  <si>
+    <t>检查类型</t>
+  </si>
+  <si>
+    <t>檢查類型</t>
+  </si>
+  <si>
+    <t>Tipo de regra</t>
+  </si>
+  <si>
+    <t>Tipo de regla</t>
+  </si>
+  <si>
+    <t>ana_fps</t>
+  </si>
+  <si>
+    <t>FPS</t>
+  </si>
+  <si>
+    <t>帧率</t>
+  </si>
+  <si>
+    <t>幀率</t>
+  </si>
+  <si>
+    <t>ana_priority</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>级别</t>
+  </si>
+  <si>
+    <t>級別</t>
+  </si>
+  <si>
+    <t>Prioridade</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
+  </si>
+  <si>
+    <t>ana_please_similarity</t>
+  </si>
+  <si>
+    <t>Similarity threshold</t>
+  </si>
+  <si>
+    <t>相似阈值</t>
+  </si>
+  <si>
+    <t>相似閾值</t>
+  </si>
+  <si>
+    <t>limiar de semelhança</t>
+  </si>
+  <si>
+    <t>Umbral de similitud</t>
+  </si>
+  <si>
+    <t>ana_please_min_size</t>
+  </si>
+  <si>
+    <t>Min size</t>
+  </si>
+  <si>
+    <t>最小尺寸</t>
+  </si>
+  <si>
+    <t>Tamanho mínimo</t>
+  </si>
+  <si>
+    <t>Tamaño mínimo</t>
+  </si>
+  <si>
+    <t>ana_license_plate_min_size</t>
+  </si>
+  <si>
+    <t>License plate min size</t>
+  </si>
+  <si>
+    <t>车牌最小尺寸</t>
+  </si>
+  <si>
+    <t>車牌最小尺寸</t>
+  </si>
+  <si>
+    <t>Tamanho mínimo da placa</t>
+  </si>
+  <si>
+    <t>Tamaño mínimo de la matrícula</t>
+  </si>
+  <si>
+    <t>ana_license_plate_max_size</t>
+  </si>
+  <si>
+    <t>License plate max size</t>
+  </si>
+  <si>
+    <t>车牌最大尺寸</t>
+  </si>
+  <si>
+    <t>車牌最大尺寸</t>
+  </si>
+  <si>
+    <t>Tamanho máximo da placa</t>
+  </si>
+  <si>
+    <t>Tamaño máximo de la matrícula</t>
+  </si>
+  <si>
+    <t>ana_more_settings</t>
+  </si>
+  <si>
+    <t>More settings</t>
+  </si>
+  <si>
+    <t>更多设置</t>
+  </si>
+  <si>
+    <t>更多設置</t>
+  </si>
+  <si>
+    <t>Mais configurações</t>
+  </si>
+  <si>
+    <t>Más configuraciones</t>
   </si>
 </sst>
 </file>
@@ -4374,6 +5124,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4387,9 +5140,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4743,7 +5493,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G232"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="31.95" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.775" style="1" customWidth="1"/>
@@ -4824,209 +5574,209 @@
     </row>
     <row r="4" customHeight="1" spans="1:7">
       <c r="A4" s="2"/>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:7">
       <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:7">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:7">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="G8" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:7">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="G9" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:7">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:7">
       <c r="A11" s="2"/>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:7">
       <c r="A12" s="2"/>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:7">
       <c r="A13" s="2"/>
       <c r="B13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>73</v>
@@ -5034,19 +5784,19 @@
     </row>
     <row r="14" customHeight="1" spans="1:7">
       <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>78</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -5064,450 +5814,450 @@
       <c r="D15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:7">
       <c r="A16" s="2"/>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="G16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F16" s="5" t="s">
+    </row>
+    <row r="17" customHeight="1" spans="1:7">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:7">
-      <c r="A17" s="6" t="s">
+      <c r="D17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="E17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="F17" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="G17" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="3" t="s">
+    </row>
+    <row r="18" customHeight="1" spans="1:7">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:7">
-      <c r="A18" s="6"/>
-      <c r="B18" s="3" t="s">
+      <c r="E18" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="3" t="s">
+    </row>
+    <row r="19" customHeight="1" spans="1:7">
+      <c r="A19" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:7">
-      <c r="A19" s="6"/>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="3" t="s">
+    </row>
+    <row r="20" customHeight="1" spans="1:7">
+      <c r="A20" s="7"/>
+      <c r="B20" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:7">
-      <c r="A20" s="6"/>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F20" s="3" t="s">
+    </row>
+    <row r="21" customHeight="1" spans="1:7">
+      <c r="A21" s="7"/>
+      <c r="B21" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:7">
-      <c r="A21" s="6"/>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F21" s="3" t="s">
+    </row>
+    <row r="22" customHeight="1" spans="1:7">
+      <c r="A22" s="7"/>
+      <c r="B22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:7">
-      <c r="A22" s="6"/>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F22" s="3" t="s">
+    </row>
+    <row r="23" customHeight="1" spans="1:7">
+      <c r="A23" s="7"/>
+      <c r="B23" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:7">
-      <c r="A23" s="6"/>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G23" s="3" t="s">
+    </row>
+    <row r="24" customHeight="1" spans="1:7">
+      <c r="A24" s="7"/>
+      <c r="B24" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:7">
-      <c r="A24" s="6"/>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G24" s="3" t="s">
+    </row>
+    <row r="25" customHeight="1" spans="1:7">
+      <c r="A25" s="7"/>
+      <c r="B25" s="3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:7">
-      <c r="A25" s="6"/>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F25" s="3" t="s">
+    </row>
+    <row r="26" customHeight="1" spans="1:7">
+      <c r="A26" s="7"/>
+      <c r="B26" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:7">
-      <c r="A26" s="6"/>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F26" s="3" t="s">
+    </row>
+    <row r="27" customHeight="1" spans="1:7">
+      <c r="A27" s="7"/>
+      <c r="B27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:7">
-      <c r="A27" s="6"/>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="3" t="s">
+    </row>
+    <row r="28" customHeight="1" spans="1:7">
+      <c r="A28" s="7"/>
+      <c r="B28" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:7">
-      <c r="A28" s="6"/>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F28" s="3" t="s">
+    </row>
+    <row r="29" customHeight="1" spans="1:7">
+      <c r="A29" s="7"/>
+      <c r="B29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:7">
-      <c r="A29" s="6"/>
-      <c r="B29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="F29" s="3" t="s">
+    </row>
+    <row r="30" customHeight="1" spans="1:7">
+      <c r="A30" s="7"/>
+      <c r="B30" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:7">
-      <c r="A30" s="6"/>
-      <c r="B30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F30" s="3" t="s">
+    </row>
+    <row r="31" customHeight="1" spans="1:7">
+      <c r="A31" s="7"/>
+      <c r="B31" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:7">
-      <c r="A31" s="6"/>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:7">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C32" s="7" t="s">
+      <c r="A32" s="7"/>
+      <c r="B32" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="D32" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="E32" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="F32" s="3" t="s">
         <v>184</v>
       </c>
+      <c r="G32" s="3" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="33" customHeight="1" spans="1:7">
-      <c r="A33" s="6"/>
+      <c r="A33" s="7"/>
       <c r="B33" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:7">
+      <c r="A34" s="7"/>
+      <c r="B34" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:7">
-      <c r="A34" s="6" t="s">
+      <c r="D34" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="F34" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="G34" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F34" s="3" t="s">
+    </row>
+    <row r="35" customHeight="1" spans="1:7">
+      <c r="A35" s="7"/>
+      <c r="B35" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:7">
-      <c r="A35" s="6"/>
-      <c r="B35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="E35" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="F35" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>200</v>
-      </c>
     </row>
     <row r="36" customHeight="1" spans="1:7">
-      <c r="A36" s="6"/>
+      <c r="A36" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="B36" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>204</v>
@@ -5520,7 +6270,7 @@
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:7">
-      <c r="A37" s="6"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="3" t="s">
         <v>207</v>
       </c>
@@ -5537,19 +6287,19 @@
         <v>210</v>
       </c>
       <c r="G37" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:7">
+      <c r="A38" s="7"/>
+      <c r="B38" s="3" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:7">
-      <c r="A38" s="6"/>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>214</v>
@@ -5562,7 +6312,7 @@
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:7">
-      <c r="A39" s="6"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="3" t="s">
         <v>217</v>
       </c>
@@ -5583,7 +6333,7 @@
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:7">
-      <c r="A40" s="6"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="3" t="s">
         <v>222</v>
       </c>
@@ -5594,17 +6344,17 @@
         <v>224</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:7">
-      <c r="A41" s="6"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="3" t="s">
         <v>227</v>
       </c>
@@ -5621,54 +6371,54 @@
         <v>230</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:7">
-      <c r="A42" s="6"/>
+      <c r="A42" s="7"/>
       <c r="B42" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E42" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G42" s="5" t="s">
+      <c r="E42" s="3" t="s">
         <v>235</v>
       </c>
+      <c r="F42" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="1:7">
-      <c r="A43" s="6"/>
+      <c r="A43" s="7"/>
       <c r="B43" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G43" s="10" t="s">
         <v>240</v>
       </c>
+      <c r="G43" s="3" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="44" customHeight="1" spans="1:7">
-      <c r="A44" s="6"/>
-      <c r="B44" s="2" t="s">
+      <c r="A44" s="7"/>
+      <c r="B44" s="3" t="s">
         <v>241</v>
       </c>
       <c r="C44" s="3" t="s">
@@ -5677,39 +6427,39 @@
       <c r="D44" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="G44" s="5" t="s">
+    </row>
+    <row r="45" customHeight="1" spans="1:7">
+      <c r="A45" s="7"/>
+      <c r="B45" s="3" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:7">
-      <c r="A45" s="6"/>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>248</v>
-      </c>
     </row>
     <row r="46" customHeight="1" spans="1:7">
-      <c r="A46" s="6"/>
+      <c r="A46" s="7"/>
       <c r="B46" s="2" t="s">
         <v>251</v>
       </c>
@@ -5719,18 +6469,18 @@
       <c r="D46" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="6" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:7">
-      <c r="A47" s="6"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="2" t="s">
         <v>257</v>
       </c>
@@ -5740,152 +6490,152 @@
       <c r="D47" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="E47" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="F47" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:7">
+      <c r="A48" s="7"/>
+      <c r="B48" s="2" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:7">
-      <c r="A48" s="6"/>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="G48" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G48" s="3" t="s">
+    </row>
+    <row r="49" customHeight="1" spans="1:7">
+      <c r="A49" s="7"/>
+      <c r="B49" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:7">
-      <c r="A49" s="6"/>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G49" s="3" t="s">
+    </row>
+    <row r="50" customHeight="1" spans="1:7">
+      <c r="A50" s="7"/>
+      <c r="B50" s="2" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:7">
-      <c r="A50" s="6"/>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G50" s="10" t="s">
+    </row>
+    <row r="51" customHeight="1" spans="1:7">
+      <c r="A51" s="7"/>
+      <c r="B51" s="3" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="1:7">
-      <c r="A51" s="6"/>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F51" s="3" t="s">
+    </row>
+    <row r="52" customHeight="1" spans="1:7">
+      <c r="A52" s="7"/>
+      <c r="B52" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:7">
-      <c r="A52" s="6"/>
-      <c r="B52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="F52" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="G52" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="F52" s="3" t="s">
+    </row>
+    <row r="53" customHeight="1" spans="1:7">
+      <c r="A53" s="7"/>
+      <c r="B53" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="1:7">
-      <c r="A53" s="6"/>
-      <c r="B53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="G53" s="3" t="s">
+    </row>
+    <row r="54" customHeight="1" spans="1:7">
+      <c r="A54" s="7"/>
+      <c r="B54" s="3" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:7">
-      <c r="A54" s="6"/>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>298</v>
@@ -5894,32 +6644,32 @@
         <v>299</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:7">
-      <c r="A55" s="6"/>
+      <c r="A55" s="7"/>
       <c r="B55" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="E55" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="E55" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="G55" s="3" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:7">
-      <c r="A56" s="6"/>
+      <c r="A56" s="7"/>
       <c r="B56" s="3" t="s">
         <v>306</v>
       </c>
@@ -5929,18 +6679,18 @@
       <c r="D56" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>307</v>
+      <c r="G56" s="3" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:7">
-      <c r="A57" s="6"/>
+      <c r="A57" s="7"/>
       <c r="B57" s="3" t="s">
         <v>310</v>
       </c>
@@ -5950,18 +6700,18 @@
       <c r="D57" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G57" s="6" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:7">
-      <c r="A58" s="6"/>
+      <c r="A58" s="7"/>
       <c r="B58" s="3" t="s">
         <v>316</v>
       </c>
@@ -5971,102 +6721,102 @@
       <c r="D58" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:7">
+      <c r="A59" s="7"/>
+      <c r="B59" s="3" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:7">
-      <c r="A59" s="6"/>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="G59" s="5" t="s">
+    </row>
+    <row r="60" customHeight="1" spans="1:7">
+      <c r="A60" s="7"/>
+      <c r="B60" s="3" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="1:7">
-      <c r="A60" s="6"/>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="E60" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="F60" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="G60" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F60" s="5" t="s">
+    </row>
+    <row r="61" customHeight="1" spans="1:7">
+      <c r="A61" s="7"/>
+      <c r="B61" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="C61" s="3" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:7">
-      <c r="A61" s="6"/>
-      <c r="B61" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="E61" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="F61" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="G61" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="F61" s="5" t="s">
+    </row>
+    <row r="62" customHeight="1" spans="1:7">
+      <c r="A62" s="7"/>
+      <c r="B62" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:7">
-      <c r="A62" s="6"/>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="E62" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="10" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:7">
-      <c r="A63" s="6"/>
+      <c r="A63" s="7"/>
       <c r="B63" s="3" t="s">
         <v>343</v>
       </c>
@@ -6076,18 +6826,18 @@
       <c r="D63" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="F63" s="5" t="s">
+      <c r="E63" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="F63" s="6" t="s">
         <v>347</v>
       </c>
+      <c r="G63" s="6" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="64" customHeight="1" spans="1:7">
-      <c r="A64" s="6"/>
+      <c r="A64" s="7"/>
       <c r="B64" s="3" t="s">
         <v>348</v>
       </c>
@@ -6097,1297 +6847,1297 @@
       <c r="D64" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F64" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="G64" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="G64" s="5" t="s">
+    </row>
+    <row r="65" customHeight="1" spans="1:7">
+      <c r="A65" s="7"/>
+      <c r="B65" s="3" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:7">
-      <c r="A65" s="6"/>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F65" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="F65" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>326</v>
+      <c r="G65" s="10" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:7">
-      <c r="A66" s="6"/>
-      <c r="B66" s="2" t="s">
-        <v>357</v>
+      <c r="A66" s="7"/>
+      <c r="B66" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="E66" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="E66" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="F66" s="6" t="s">
         <v>362</v>
       </c>
+      <c r="G66" s="6" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="67" customHeight="1" spans="1:7">
-      <c r="A67" s="6" t="s">
-        <v>363</v>
-      </c>
+      <c r="A67" s="7"/>
       <c r="B67" s="2" t="s">
         <v>364</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="F67" s="5" t="s">
+      <c r="F67" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:7">
+      <c r="A68" s="7"/>
+      <c r="B68" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="C68" s="3" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:7">
-      <c r="A68" s="6"/>
-      <c r="B68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="E68" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="F68" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="G68" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="F68" s="3" t="s">
+    </row>
+    <row r="69" customHeight="1" spans="1:7">
+      <c r="A69" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:7">
-      <c r="A69" s="6"/>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F69" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="G69" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="F69" s="5" t="s">
+    </row>
+    <row r="70" customHeight="1" spans="1:7">
+      <c r="A70" s="7"/>
+      <c r="B70" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="C70" s="3" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:7">
-      <c r="A70" s="6"/>
-      <c r="B70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="G70" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="F70" s="5" t="s">
+    </row>
+    <row r="71" customHeight="1" spans="1:7">
+      <c r="A71" s="7"/>
+      <c r="B71" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="C71" s="3" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="71" customHeight="1" spans="1:7">
-      <c r="A71" s="6"/>
-      <c r="B71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="E71" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="F71" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="G71" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="F71" s="5" t="s">
+    </row>
+    <row r="72" customHeight="1" spans="1:7">
+      <c r="A72" s="7"/>
+      <c r="B72" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="G71" s="5" t="s">
+      <c r="C72" s="3" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:7">
-      <c r="A72" s="6"/>
-      <c r="B72" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="E72" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="F72" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="G72" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="F72" s="5" t="s">
+    </row>
+    <row r="73" customHeight="1" spans="1:7">
+      <c r="A73" s="7"/>
+      <c r="B73" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="C73" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:7">
-      <c r="A73" s="6"/>
-      <c r="B73" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="E73" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="F73" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="G73" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F73" s="5" t="s">
+    </row>
+    <row r="74" customHeight="1" spans="1:7">
+      <c r="A74" s="7"/>
+      <c r="B74" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="C74" s="3" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:7">
-      <c r="A74" s="6"/>
-      <c r="B74" s="2" t="s">
+      <c r="D74" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="E74" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="F74" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="G74" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="F74" s="2" t="s">
+    </row>
+    <row r="75" customHeight="1" spans="1:7">
+      <c r="A75" s="7"/>
+      <c r="B75" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="1:7">
-      <c r="A75" s="6"/>
-      <c r="B75" s="2" t="s">
+      <c r="D75" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="E75" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="F75" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="G75" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="F75" s="5" t="s">
+    </row>
+    <row r="76" customHeight="1" spans="1:7">
+      <c r="A76" s="7"/>
+      <c r="B76" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="G75" s="5" t="s">
+      <c r="C76" s="2" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="76" customHeight="1" spans="1:7">
-      <c r="A76" s="6" t="s">
+      <c r="D76" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="E76" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="G76" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:7">
+      <c r="A77" s="7"/>
+      <c r="B77" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="F76" s="5" t="s">
+      <c r="C77" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="D77" s="2" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:7">
-      <c r="A77" s="6"/>
-      <c r="B77" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>220</v>
+      <c r="F77" s="2" t="s">
+        <v>423</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>221</v>
+        <v>424</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:7">
-      <c r="A78" s="6"/>
+      <c r="A78" s="7"/>
       <c r="B78" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="G78" s="3" t="s">
         <v>427</v>
       </c>
+      <c r="E78" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="79" customHeight="1" spans="1:7">
-      <c r="A79" s="6"/>
+      <c r="A79" s="7" t="s">
+        <v>431</v>
+      </c>
       <c r="B79" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="G79" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:7">
+      <c r="A80" s="7"/>
+      <c r="B80" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:7">
+      <c r="A81" s="7"/>
+      <c r="B81" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:7">
+      <c r="A82" s="7"/>
+      <c r="B82" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:7">
+      <c r="A83" s="7"/>
+      <c r="B83" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="1:7">
+      <c r="A84" s="7"/>
+      <c r="B84" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="1:7">
+      <c r="A85" s="7"/>
+      <c r="B85" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="1:7">
+      <c r="A86" s="7"/>
+      <c r="B86" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="1:7">
+      <c r="A87" s="7"/>
+      <c r="B87" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="1:7">
+      <c r="A88" s="7"/>
+      <c r="B88" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:7">
+      <c r="A89" s="7"/>
+      <c r="B89" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="1:7">
+      <c r="A90" s="7"/>
+      <c r="B90" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="1:7">
+      <c r="A91" s="7"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:7">
+      <c r="A92" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="1:7">
+      <c r="A93" s="7"/>
+      <c r="B93" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:7">
+      <c r="A94" s="7"/>
+      <c r="B94" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:7">
+      <c r="A95" s="7"/>
+      <c r="B95" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:7">
+      <c r="A96" s="7"/>
+      <c r="B96" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:7">
+      <c r="A97" s="7" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:7">
-      <c r="A80" s="6"/>
-      <c r="B80" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:7">
-      <c r="A81" s="6"/>
-      <c r="B81" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:7">
-      <c r="A82" s="6"/>
-      <c r="B82" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:7">
-      <c r="A83" s="6"/>
-      <c r="B83" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="84" customHeight="1" spans="1:7">
-      <c r="A84" s="6"/>
-      <c r="B84" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="85" customHeight="1" spans="1:7">
-      <c r="A85" s="6"/>
-      <c r="B85" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="1:7">
-      <c r="A86" s="6"/>
-      <c r="B86" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="87" customHeight="1" spans="1:7">
-      <c r="A87" s="6"/>
-      <c r="B87" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="88" customHeight="1" spans="1:7">
-      <c r="A88" s="6"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-    </row>
-    <row r="89" customHeight="1" spans="1:7">
-      <c r="A89" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="90" customHeight="1" spans="1:7">
-      <c r="A90" s="6"/>
-      <c r="B90" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="91" customHeight="1" spans="1:7">
-      <c r="A91" s="6"/>
-      <c r="B91" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="92" customHeight="1" spans="1:7">
-      <c r="A92" s="6"/>
-      <c r="B92" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="93" customHeight="1" spans="1:7">
-      <c r="A93" s="6"/>
-      <c r="B93" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="94" customHeight="1" spans="1:7">
-      <c r="A94" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="95" customHeight="1" spans="1:7">
-      <c r="A95" s="6"/>
-      <c r="B95" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="96" customHeight="1" spans="1:7">
-      <c r="A96" s="6"/>
-      <c r="B96" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="D96" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="C97" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="D97" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="E97" s="2" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="97" customHeight="1" spans="1:7">
-      <c r="A97" s="6"/>
-      <c r="B97" s="3" t="s">
+      <c r="F97" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="G97" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="D97" s="3" t="s">
+    </row>
+    <row r="98" customHeight="1" spans="1:7">
+      <c r="A98" s="7"/>
+      <c r="B98" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="C98" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="D98" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="G97" s="5" t="s">
+      <c r="E98" s="6" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="98" customHeight="1" spans="1:7">
-      <c r="A98" s="6"/>
-      <c r="B98" s="3" t="s">
+      <c r="F98" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="G98" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="D98" s="3" t="s">
+    </row>
+    <row r="99" customHeight="1" spans="1:7">
+      <c r="A99" s="7"/>
+      <c r="B99" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="E98" s="5" t="s">
+      <c r="C99" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F98" s="5" t="s">
+      <c r="D99" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="E99" s="6" t="s">
         <v>538</v>
       </c>
-    </row>
-    <row r="99" customHeight="1" spans="1:7">
-      <c r="A99" s="6"/>
-      <c r="B99" s="2" t="s">
+      <c r="F99" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="G99" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="D99" s="2" t="s">
+    </row>
+    <row r="100" customHeight="1" spans="1:7">
+      <c r="A100" s="7"/>
+      <c r="B100" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="C100" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="D100" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="E100" s="6" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:7">
-      <c r="A100" s="6"/>
+      <c r="F100" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="101" customHeight="1" spans="1:7">
-      <c r="A101" s="6"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>552</v>
+      </c>
     </row>
     <row r="102" customHeight="1" spans="1:7">
-      <c r="A102" s="6"/>
+      <c r="A102" s="7"/>
+      <c r="B102" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="103" customHeight="1" spans="1:7">
-      <c r="A103" s="6"/>
+      <c r="A103" s="7"/>
     </row>
     <row r="104" customHeight="1" spans="1:7">
-      <c r="A104" s="6"/>
+      <c r="A104" s="7"/>
     </row>
     <row r="105" customHeight="1" spans="1:7">
-      <c r="A105" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>550</v>
-      </c>
+      <c r="A105" s="7"/>
     </row>
     <row r="106" customHeight="1" spans="1:7">
-      <c r="A106" s="6"/>
-      <c r="B106" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>556</v>
-      </c>
+      <c r="A106" s="7"/>
     </row>
     <row r="107" customHeight="1" spans="1:7">
-      <c r="A107" s="6"/>
-      <c r="B107" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D107" s="3" t="s">
+      <c r="A107" s="7"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:7">
+      <c r="A108" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="C108" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="D108" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="E108" s="6" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="108" customHeight="1" spans="1:7">
-      <c r="A108" s="6"/>
-      <c r="B108" s="3" t="s">
+      <c r="F108" s="6" t="s">
         <v>563</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="G108" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="D108" s="3" t="s">
+    </row>
+    <row r="109" customHeight="1" spans="1:7">
+      <c r="A109" s="7"/>
+      <c r="B109" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="C109" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="F108" s="5" t="s">
+      <c r="D109" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="E109" s="6" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="109" customHeight="1" spans="1:7">
-      <c r="A109" s="6"/>
-      <c r="B109" s="3" t="s">
+      <c r="F109" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="G109" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="D109" s="3" t="s">
+    </row>
+    <row r="110" customHeight="1" spans="1:7">
+      <c r="A110" s="7"/>
+      <c r="B110" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="C110" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="F109" s="5" t="s">
+      <c r="D110" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="E110" s="6" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="110" customHeight="1" spans="1:7">
-      <c r="A110" s="6"/>
-      <c r="B110" s="3" t="s">
+      <c r="F110" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="G110" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="D110" s="3" t="s">
+    </row>
+    <row r="111" customHeight="1" spans="1:7">
+      <c r="A111" s="7"/>
+      <c r="B111" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="D111" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="E111" s="6" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="111" customHeight="1" spans="1:7">
-      <c r="A111" s="6"/>
-      <c r="B111" s="2" t="s">
+      <c r="F111" s="6" t="s">
         <v>581</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="G111" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="D111" s="3" t="s">
+    </row>
+    <row r="112" customHeight="1" spans="1:7">
+      <c r="A112" s="7"/>
+      <c r="B112" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="F111" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="G111" s="10" t="s">
+      <c r="D112" s="3" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="112" customHeight="1" spans="1:7">
-      <c r="A112" s="6"/>
-      <c r="B112" s="2" t="s">
+      <c r="E112" s="6" t="s">
         <v>586</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="F112" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="G112" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="E112" s="3" t="s">
+    </row>
+    <row r="113" customHeight="1" spans="1:7">
+      <c r="A113" s="7"/>
+      <c r="B113" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="C113" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="113" customHeight="1" spans="1:7">
-      <c r="A113" s="6"/>
-      <c r="B113" s="2" t="s">
+      <c r="E113" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="F113" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="G113" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="E113" s="3" t="s">
+    </row>
+    <row r="114" customHeight="1" spans="1:7">
+      <c r="A114" s="7"/>
+      <c r="B114" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="C114" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="G113" s="3" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="114" customHeight="1" spans="1:7">
-      <c r="A114" s="6"/>
-      <c r="B114" s="3" t="s">
+      <c r="D114" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="E114" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="F114" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="G114" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="E114" s="5" t="s">
+    </row>
+    <row r="115" customHeight="1" spans="1:7">
+      <c r="A115" s="7"/>
+      <c r="B115" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="F114" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="G114" s="5" t="s">
+      <c r="C115" s="3" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="115" customHeight="1" spans="1:7">
-      <c r="A115" s="6"/>
-      <c r="B115" s="2" t="s">
+      <c r="D115" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="E115" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="F115" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>601</v>
+      <c r="F115" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:7">
-      <c r="A116" s="6"/>
-      <c r="B116" s="3" t="s">
-        <v>604</v>
+      <c r="A116" s="7"/>
+      <c r="B116" s="2" t="s">
+        <v>606</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="F116" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="E116" s="3" t="s">
         <v>609</v>
       </c>
+      <c r="F116" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="117" customHeight="1" spans="1:7">
-      <c r="A117" s="6"/>
+      <c r="A117" s="7"/>
       <c r="B117" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D117" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F117" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="E117" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="G117" s="5" t="s">
+      <c r="G117" s="6" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:7">
-      <c r="A118" s="6"/>
-      <c r="B118" s="3" t="s">
+      <c r="A118" s="7"/>
+      <c r="B118" s="2" t="s">
         <v>616</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>617</v>
       </c>
       <c r="D118" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="1:7">
+      <c r="A119" s="7"/>
+      <c r="B119" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="C119" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="D119" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="E119" s="6" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="119" customHeight="1" spans="1:7">
-      <c r="A119" s="6"/>
-      <c r="B119" s="3" t="s">
+      <c r="F119" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="G119" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="D119" s="3" t="s">
+    </row>
+    <row r="120" customHeight="1" spans="1:7">
+      <c r="A120" s="7"/>
+      <c r="B120" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="C120" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="D120" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="E120" s="6" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="120" customHeight="1" spans="1:7">
-      <c r="A120" s="6"/>
-      <c r="B120" s="3" t="s">
+      <c r="F120" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="G120" s="6" t="s">
         <v>629</v>
       </c>
-      <c r="D120" s="3" t="s">
+    </row>
+    <row r="121" customHeight="1" spans="1:7">
+      <c r="A121" s="7"/>
+      <c r="B121" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="E120" s="5" t="s">
+      <c r="C121" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="F120" s="5" t="s">
+      <c r="D121" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="G120" s="5" t="s">
+      <c r="E121" s="6" t="s">
         <v>633</v>
       </c>
-    </row>
-    <row r="121" customHeight="1" spans="1:7">
-      <c r="A121" s="6"/>
-      <c r="B121" s="3" t="s">
+      <c r="F121" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="G121" s="6" t="s">
         <v>635</v>
       </c>
-      <c r="D121" s="3" t="s">
+    </row>
+    <row r="122" customHeight="1" spans="1:7">
+      <c r="A122" s="7"/>
+      <c r="B122" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="E121" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="F121" s="5" t="s">
+      <c r="C122" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="G121" s="5" t="s">
+      <c r="D122" s="3" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="122" customHeight="1" spans="1:7">
-      <c r="A122" s="6"/>
+      <c r="E122" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="123" customHeight="1" spans="1:7">
-      <c r="A123" s="6"/>
+      <c r="A123" s="7"/>
+      <c r="B123" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="124" customHeight="1" spans="1:7">
-      <c r="A124" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="G124" s="3" t="s">
-        <v>644</v>
+      <c r="A124" s="7"/>
+      <c r="B124" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:7">
-      <c r="A125" s="6"/>
+      <c r="A125" s="7"/>
       <c r="B125" s="3" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="F125" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>650</v>
+        <v>656</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:7">
-      <c r="A126" s="6"/>
-      <c r="B126" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="F126" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>655</v>
-      </c>
+      <c r="A126" s="7"/>
     </row>
     <row r="127" customHeight="1" spans="1:7">
-      <c r="A127" s="6"/>
-      <c r="B127" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="E127" s="3" t="s">
+      <c r="A127" s="7"/>
+    </row>
+    <row r="128" customHeight="1" spans="1:7">
+      <c r="A128" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="G127" s="3" t="s">
+      <c r="C128" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="128" customHeight="1" spans="1:7">
-      <c r="A128" s="6"/>
-      <c r="B128" s="3" t="s">
+      <c r="E128" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="F128" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="G128" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="E128" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="F128" s="3" t="s">
+    </row>
+    <row r="129" customHeight="1" spans="1:7">
+      <c r="A129" s="7"/>
+      <c r="B129" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="G128" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="129" customHeight="1" spans="1:7">
-      <c r="A129" s="6"/>
-      <c r="B129" s="3" t="s">
+      <c r="D129" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="E129" s="6" t="s">
         <v>668</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="F129" s="6" t="s">
         <v>669</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="G129" s="6" t="s">
         <v>670</v>
       </c>
-      <c r="F129" s="3" t="s">
+    </row>
+    <row r="130" customHeight="1" spans="1:7">
+      <c r="A130" s="7"/>
+      <c r="B130" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="G129" s="3" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="130" customHeight="1" spans="1:7">
-      <c r="A130" s="6"/>
-      <c r="B130" s="3" t="s">
+      <c r="C130" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="D130" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="E130" s="6" t="s">
         <v>674</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="F130" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="F130" s="5" t="s">
+      <c r="G130" s="6" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:7">
+      <c r="A131" s="7"/>
+      <c r="B131" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" spans="1:7">
-      <c r="A131" s="6"/>
-      <c r="B131" s="3" t="s">
+      <c r="C131" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="D131" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="E131" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="E131" s="5" t="s">
-        <v>679</v>
-      </c>
-      <c r="F131" s="5" t="s">
+      <c r="F131" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="G131" s="5" t="s">
+      <c r="G131" s="3" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:7">
-      <c r="A132" s="6"/>
+      <c r="A132" s="7"/>
       <c r="B132" s="3" t="s">
         <v>682</v>
       </c>
@@ -7397,1548 +8147,1548 @@
       <c r="D132" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="E132" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="F132" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="F132" s="5" t="s">
+      <c r="G132" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="G132" s="5" t="s">
+    </row>
+    <row r="133" customHeight="1" spans="1:7">
+      <c r="A133" s="7"/>
+      <c r="B133" s="3" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="133" customHeight="1" spans="1:7">
-      <c r="A133" s="6"/>
-      <c r="B133" s="3" t="s">
+      <c r="C133" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="D133" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="E133" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="E133" s="5" t="s">
+      <c r="F133" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="F133" s="5" t="s">
+      <c r="G133" s="3" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="1:7">
+      <c r="A134" s="7"/>
+      <c r="B134" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="G133" s="5" t="s">
+      <c r="C134" s="3" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="134" customHeight="1" spans="1:7">
-      <c r="A134" s="6" t="s">
+      <c r="D134" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="E134" s="6" t="s">
         <v>695</v>
       </c>
-      <c r="C134" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="D134" s="3" t="s">
+      <c r="F134" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="E134" s="3" t="s">
+      <c r="G134" s="6" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="1:7">
+      <c r="A135" s="7"/>
+      <c r="B135" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="C135" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="G134" s="3" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" spans="1:7">
-      <c r="A135" s="6"/>
-      <c r="B135" s="3" t="s">
+      <c r="D135" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="C135" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D135" s="3" t="s">
+      <c r="E135" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="F135" s="6" t="s">
         <v>700</v>
       </c>
-      <c r="E135" s="5" t="s">
+      <c r="G135" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="F135" s="5" t="s">
+    </row>
+    <row r="136" customHeight="1" spans="1:7">
+      <c r="A136" s="7"/>
+      <c r="B136" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="G135" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="136" customHeight="1" spans="1:7">
-      <c r="A136" s="6"/>
-      <c r="B136" s="3" t="s">
+      <c r="C136" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="D136" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="E136" s="6" t="s">
         <v>705</v>
       </c>
-      <c r="E136" s="3" t="s">
+      <c r="F136" s="6" t="s">
         <v>706</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="G136" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="G136" s="3" t="s">
+    </row>
+    <row r="137" customHeight="1" spans="1:7">
+      <c r="A137" s="7"/>
+      <c r="B137" s="3" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="137" customHeight="1" spans="1:7">
-      <c r="A137" s="6"/>
-      <c r="B137" s="5" t="s">
+      <c r="C137" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="D137" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="E137" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="F137" s="6" t="s">
         <v>712</v>
       </c>
-      <c r="F137" s="5" t="s">
+      <c r="G137" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="G137" s="5" t="s">
+    </row>
+    <row r="138" customHeight="1" spans="1:7">
+      <c r="A138" s="7" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="138" customHeight="1" spans="1:7">
-      <c r="A138" s="6"/>
-      <c r="B138" s="5" t="s">
+      <c r="B138" s="3" t="s">
         <v>715</v>
       </c>
       <c r="C138" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="E138" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="F138" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="G138" s="3" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="1:7">
+      <c r="A139" s="7"/>
+      <c r="B139" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="G138" s="5" t="s">
+      <c r="C139" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D139" s="3" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="139" customHeight="1" spans="1:7">
-      <c r="A139" s="6"/>
-      <c r="B139" s="5" t="s">
+      <c r="E139" s="6" t="s">
         <v>721</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="F139" s="6" t="s">
         <v>722</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="G139" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="1:7">
+      <c r="A140" s="7"/>
+      <c r="B140" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="E139" s="5" t="s">
+      <c r="C140" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="F139" s="5" t="s">
+      <c r="D140" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="G139" s="5" t="s">
+      <c r="E140" s="3" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="140" customHeight="1" spans="1:7">
-      <c r="A140" s="6"/>
-      <c r="B140" s="2" t="s">
+      <c r="F140" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="G140" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="D140" s="2" t="s">
+    </row>
+    <row r="141" customHeight="1" spans="1:7">
+      <c r="A141" s="7"/>
+      <c r="B141" s="6" t="s">
         <v>729</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="C141" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="D141" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="E141" s="6" t="s">
         <v>732</v>
       </c>
-    </row>
-    <row r="141" customHeight="1" spans="1:7">
-      <c r="A141" s="6"/>
-      <c r="B141" s="2" t="s">
+      <c r="F141" s="6" t="s">
         <v>733</v>
       </c>
-      <c r="C141" s="2" t="s">
+      <c r="G141" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="D141" s="2" t="s">
+    </row>
+    <row r="142" customHeight="1" spans="1:7">
+      <c r="A142" s="7"/>
+      <c r="B142" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="C142" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="F141" s="2" t="s">
+      <c r="D142" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="G141" s="3" t="s">
+      <c r="E142" s="6" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="142" customHeight="1" spans="1:7">
-      <c r="A142" s="6"/>
-      <c r="B142" s="2" t="s">
+      <c r="F142" s="6" t="s">
         <v>739</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="G142" s="6" t="s">
         <v>740</v>
       </c>
-      <c r="D142" s="2" t="s">
+    </row>
+    <row r="143" customHeight="1" spans="1:7">
+      <c r="A143" s="7"/>
+      <c r="B143" s="6" t="s">
         <v>741</v>
       </c>
-      <c r="E142" s="2" t="s">
+      <c r="C143" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="F142" s="2" t="s">
+      <c r="D143" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="E143" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="G143" s="6" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:7">
+      <c r="A144" s="7"/>
+      <c r="B144" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="1:7">
+      <c r="A145" s="7"/>
+      <c r="B145" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="1:7">
+      <c r="A146" s="7"/>
+      <c r="B146" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="1:7">
+      <c r="A147" s="7"/>
+      <c r="B147" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="1:7">
+      <c r="A148" s="7"/>
+      <c r="B148" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:7">
+      <c r="A149" s="7"/>
+      <c r="B149" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="143" customHeight="1" spans="1:7">
-      <c r="A143" s="6"/>
-      <c r="B143" s="2" t="s">
+      <c r="E149" s="6" t="s">
         <v>744</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D143" s="2" t="s">
+      <c r="F149" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="G149" s="6" t="s">
         <v>746</v>
       </c>
-      <c r="F143" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" spans="1:7">
-      <c r="A144" s="6"/>
-      <c r="B144" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" spans="1:7">
-      <c r="A145" s="6"/>
-      <c r="B145" s="5" t="s">
-        <v>753</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>724</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" spans="1:7">
-      <c r="A146" s="6"/>
-      <c r="B146" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" spans="1:7">
-      <c r="A147" s="6"/>
-      <c r="B147" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" spans="1:7">
-      <c r="A148" s="6"/>
-      <c r="B148" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="G148" s="3" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" spans="1:7">
-      <c r="A149" s="6"/>
-      <c r="B149" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="D149" s="3" t="s">
+    </row>
+    <row r="150" customHeight="1" spans="1:7">
+      <c r="A150" s="7"/>
+      <c r="B150" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="E149" s="5" t="s">
+      <c r="C150" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="F149" s="5" t="s">
+      <c r="D150" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="G149" s="5" t="s">
+      <c r="E150" s="2" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="150" customHeight="1" spans="1:7">
-      <c r="A150" s="6"/>
-      <c r="B150" s="2" t="s">
+      <c r="F150" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="G150" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="D150" s="2" t="s">
+    </row>
+    <row r="151" customHeight="1" spans="1:7">
+      <c r="A151" s="7"/>
+      <c r="B151" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="F150" s="2" t="s">
+      <c r="C151" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="G150" s="3" t="s">
+      <c r="D151" s="3" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="151" customHeight="1" spans="1:7">
-      <c r="A151" s="6"/>
-      <c r="B151" s="2" t="s">
+      <c r="E151" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="C151" s="2" t="s">
+      <c r="F151" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="D151" s="2" t="s">
+      <c r="G151" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="E151" s="2" t="s">
+    </row>
+    <row r="152" customHeight="1" spans="1:7">
+      <c r="A152" s="7"/>
+      <c r="B152" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="C152" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="G151" s="10" t="s">
+      <c r="D152" s="2" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="152" customHeight="1" spans="1:7">
-      <c r="A152" s="6"/>
-      <c r="B152" s="2" t="s">
+      <c r="E152" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="F152" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="G152" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="E152" s="2" t="s">
+    </row>
+    <row r="153" customHeight="1" spans="1:7">
+      <c r="A153" s="7"/>
+      <c r="B153" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="C153" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="G152" s="3" t="s">
+      <c r="D153" s="3" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="153" customHeight="1" spans="1:7">
-      <c r="A153" s="6"/>
-      <c r="B153" s="2" t="s">
+      <c r="E153" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="C153" s="2" t="s">
+      <c r="F153" s="6" t="s">
         <v>796</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="G153" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="E153" s="11" t="s">
+    </row>
+    <row r="154" customHeight="1" spans="1:7">
+      <c r="A154" s="7"/>
+      <c r="B154" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="F153" s="11" t="s">
+      <c r="C154" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="G153" s="5" t="s">
+      <c r="D154" s="2" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="154" customHeight="1" spans="1:7">
-      <c r="A154" s="6"/>
-      <c r="B154" s="2" t="s">
+      <c r="E154" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="C154" s="3" t="s">
+      <c r="G154" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="D154" s="3" t="s">
+    </row>
+    <row r="155" customHeight="1" spans="1:7">
+      <c r="A155" s="7"/>
+      <c r="B155" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="C155" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="D155" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="G154" s="5" t="s">
+      <c r="E155" s="2" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="155" customHeight="1" spans="1:7">
-      <c r="A155" s="6"/>
-      <c r="B155" s="2" t="s">
+      <c r="F155" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="G155" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="D155" s="2" t="s">
+    </row>
+    <row r="156" customHeight="1" spans="1:7">
+      <c r="A156" s="7"/>
+      <c r="B156" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="E155" s="2" t="s">
+      <c r="C156" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="D156" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="G155" s="3" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" spans="1:7">
-      <c r="A156" s="6"/>
-      <c r="B156" s="2" t="s">
+      <c r="E156" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="C156" s="2" t="s">
+      <c r="F156" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="D156" s="2" t="s">
+      <c r="G156" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="E156" s="2" t="s">
+    </row>
+    <row r="157" customHeight="1" spans="1:7">
+      <c r="A157" s="7"/>
+      <c r="B157" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="F156" s="2" t="s">
+      <c r="C157" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="G156" s="3" t="s">
+      <c r="D157" s="2" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="157" customHeight="1" spans="1:7">
-      <c r="A157" s="6"/>
-      <c r="B157" s="2" t="s">
+      <c r="E157" s="11" t="s">
         <v>818</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="F157" s="11" t="s">
         <v>819</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="G157" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="E157" s="3" t="s">
+    </row>
+    <row r="158" customHeight="1" spans="1:7">
+      <c r="A158" s="7"/>
+      <c r="B158" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="F157" s="3" t="s">
+      <c r="C158" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="G157" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="158" customHeight="1" spans="1:7">
-      <c r="A158" s="6"/>
-      <c r="B158" s="2" t="s">
+      <c r="D158" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="E158" s="6" t="s">
         <v>824</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="F158" s="6" t="s">
         <v>825</v>
       </c>
-      <c r="E158" s="3" t="s">
+      <c r="G158" s="6" t="s">
         <v>826</v>
       </c>
-      <c r="F158" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G158" s="3" t="s">
+    </row>
+    <row r="159" customHeight="1" spans="1:7">
+      <c r="A159" s="7"/>
+      <c r="B159" s="2" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="159" customHeight="1" spans="1:7">
-      <c r="A159" s="6"/>
-      <c r="B159" s="2" t="s">
+      <c r="C159" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="D159" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="E159" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="E159" s="3" t="s">
+      <c r="F159" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="F159" s="3" t="s">
+      <c r="G159" s="3" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:7">
+      <c r="A160" s="7"/>
+      <c r="B160" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="G159" s="3" t="s">
+      <c r="C160" s="2" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="160" customHeight="1" spans="1:7">
-      <c r="A160" s="6"/>
-      <c r="B160" s="2" t="s">
+      <c r="D160" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="E160" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="F160" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="E160" s="3" t="s">
+      <c r="G160" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="F160" s="3" t="s">
+    </row>
+    <row r="161" customHeight="1" spans="1:7">
+      <c r="A161" s="7"/>
+      <c r="B161" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="C161" s="3" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="161" customHeight="1" spans="1:7">
-      <c r="A161" s="6"/>
-      <c r="B161" s="2" t="s">
+      <c r="D161" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="E161" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="F161" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="G161" s="3" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="1:7">
+      <c r="A162" s="7"/>
+      <c r="B162" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="C162" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="G161" s="3" t="s">
+      <c r="D162" s="3" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="162" customHeight="1" spans="1:7">
-      <c r="A162" s="6"/>
-      <c r="B162" s="2" t="s">
+      <c r="E162" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="F162" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G162" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="D162" s="3" t="s">
+    </row>
+    <row r="163" customHeight="1" spans="1:7">
+      <c r="A163" s="7"/>
+      <c r="B163" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="E162" s="3" t="s">
+      <c r="C163" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="F162" s="3" t="s">
+      <c r="D163" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="G162" s="3" t="s">
+      <c r="E163" s="3" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="163" customHeight="1" spans="1:7">
-      <c r="A163" s="6"/>
-      <c r="B163" s="2" t="s">
+      <c r="F163" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="G163" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="D163" s="3" t="s">
+    </row>
+    <row r="164" customHeight="1" spans="1:7">
+      <c r="A164" s="7"/>
+      <c r="B164" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="E163" s="3" t="s">
+      <c r="C164" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="F163" s="3" t="s">
+      <c r="D164" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="G163" s="3" t="s">
+      <c r="E164" s="3" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="164" customHeight="1" spans="1:7">
-      <c r="A164" s="6"/>
-      <c r="B164" s="2" t="s">
+      <c r="F164" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="G164" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="D164" s="3" t="s">
+    </row>
+    <row r="165" customHeight="1" spans="1:7">
+      <c r="A165" s="7"/>
+      <c r="B165" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="E164" s="5" t="s">
+      <c r="C165" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="F164" s="5" t="s">
+      <c r="D165" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="G164" s="5" t="s">
+      <c r="E165" s="3" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="165" customHeight="1" spans="1:7">
-      <c r="A165" s="6"/>
-      <c r="B165" s="2" t="s">
+      <c r="F165" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="G165" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="D165" s="3" t="s">
+    </row>
+    <row r="166" customHeight="1" spans="1:7">
+      <c r="A166" s="7"/>
+      <c r="B166" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="E165" s="5" t="s">
+      <c r="C166" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="D166" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="G165" s="5" t="s">
+      <c r="E166" s="3" t="s">
         <v>869</v>
       </c>
-    </row>
-    <row r="166" customHeight="1" spans="1:7">
-      <c r="A166" s="6"/>
-      <c r="B166" s="2" t="s">
+      <c r="F166" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="G166" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="D166" s="3" t="s">
+    </row>
+    <row r="167" customHeight="1" spans="1:7">
+      <c r="A167" s="7"/>
+      <c r="B167" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="E166" s="5" t="s">
+      <c r="C167" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="F166" s="5" t="s">
+      <c r="D167" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="G166" s="5" t="s">
+      <c r="E167" s="3" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="167" customHeight="1" spans="1:7">
-      <c r="A167" s="6"/>
-      <c r="B167" s="2" t="s">
+      <c r="F167" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="G167" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="D167" s="3" t="s">
+    </row>
+    <row r="168" customHeight="1" spans="1:7">
+      <c r="A168" s="7"/>
+      <c r="B168" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="E167" s="5" t="s">
+      <c r="C168" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="D168" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="G167" s="5" t="s">
+      <c r="E168" s="6" t="s">
         <v>881</v>
       </c>
-    </row>
-    <row r="168" customHeight="1" spans="1:7">
-      <c r="A168" s="6"/>
-      <c r="B168" s="2" t="s">
+      <c r="F168" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="G168" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="D168" s="3" t="s">
+    </row>
+    <row r="169" customHeight="1" spans="1:7">
+      <c r="A169" s="7"/>
+      <c r="B169" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="E168" s="3" t="s">
+      <c r="C169" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="F168" s="3" t="s">
+      <c r="D169" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="G168" s="3" t="s">
+      <c r="E169" s="6" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="169" customHeight="1" spans="1:7">
-      <c r="A169" s="6"/>
-      <c r="B169" s="2" t="s">
+      <c r="F169" s="6" t="s">
         <v>888</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="G169" s="6" t="s">
         <v>889</v>
       </c>
-      <c r="D169" s="3" t="s">
+    </row>
+    <row r="170" customHeight="1" spans="1:7">
+      <c r="A170" s="7"/>
+      <c r="B170" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="E169" s="5" t="s">
+      <c r="C170" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="D170" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="G169" s="5" t="s">
+      <c r="E170" s="6" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="170" customHeight="1" spans="1:7">
-      <c r="A170" s="6"/>
-      <c r="B170" s="2" t="s">
+      <c r="F170" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="C170" s="3" t="s">
+      <c r="G170" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="D170" s="3" t="s">
+    </row>
+    <row r="171" customHeight="1" spans="1:7">
+      <c r="A171" s="7"/>
+      <c r="B171" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="E170" s="5" t="s">
+      <c r="C171" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="F170" s="5" t="s">
+      <c r="D171" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="G170" s="5" t="s">
+      <c r="E171" s="6" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="171" customHeight="1" spans="1:7">
-      <c r="A171" s="6"/>
-      <c r="B171" s="2" t="s">
+      <c r="F171" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="G171" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="D171" s="3" t="s">
+    </row>
+    <row r="172" customHeight="1" spans="1:7">
+      <c r="A172" s="7"/>
+      <c r="B172" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="E171" s="5" t="s">
+      <c r="C172" s="3" t="s">
         <v>903</v>
       </c>
-      <c r="F171" s="5" t="s">
+      <c r="D172" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="G171" s="5" t="s">
+      <c r="E172" s="3" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="172" customHeight="1" spans="1:7">
-      <c r="A172" s="6"/>
-      <c r="B172" s="2" t="s">
+      <c r="F172" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="C172" s="3" t="s">
+      <c r="G172" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="D172" s="3" t="s">
+    </row>
+    <row r="173" customHeight="1" spans="1:7">
+      <c r="A173" s="7"/>
+      <c r="B173" s="2" t="s">
         <v>908</v>
       </c>
-      <c r="E172" s="5" t="s">
+      <c r="C173" s="3" t="s">
         <v>909</v>
       </c>
-      <c r="F172" s="5" t="s">
+      <c r="D173" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="G172" s="5" t="s">
+      <c r="E173" s="6" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="173" customHeight="1" spans="1:7">
-      <c r="A173" s="6"/>
-      <c r="B173" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>771</v>
+      <c r="F173" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>913</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:7">
-      <c r="A174" s="6"/>
+      <c r="A174" s="7"/>
       <c r="B174" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>914</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>915</v>
-      </c>
-      <c r="F174" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="G174" s="5" t="s">
+      <c r="E174" s="6" t="s">
         <v>917</v>
       </c>
+      <c r="F174" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="G174" s="6" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="175" customHeight="1" spans="1:7">
-      <c r="A175" s="6"/>
+      <c r="A175" s="7"/>
       <c r="B175" s="2" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>921</v>
-      </c>
-      <c r="F175" s="5" t="s">
         <v>922</v>
       </c>
-      <c r="G175" s="5" t="s">
+      <c r="E175" s="6" t="s">
         <v>923</v>
       </c>
+      <c r="F175" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>925</v>
+      </c>
     </row>
     <row r="176" customHeight="1" spans="1:7">
-      <c r="A176" s="6"/>
+      <c r="A176" s="7"/>
       <c r="B176" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="E176" s="5" t="s">
-        <v>712</v>
-      </c>
-      <c r="F176" s="5" t="s">
-        <v>927</v>
-      </c>
-      <c r="G176" s="5" t="s">
         <v>928</v>
       </c>
+      <c r="E176" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="G176" s="6" t="s">
+        <v>931</v>
+      </c>
     </row>
     <row r="177" customHeight="1" spans="1:7">
-      <c r="A177" s="6"/>
+      <c r="A177" s="7"/>
       <c r="B177" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="E177" s="5" t="s">
-        <v>712</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>714</v>
+        <v>786</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:7">
-      <c r="A178" s="6"/>
+      <c r="A178" s="7"/>
       <c r="B178" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>716</v>
+        <v>933</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>718</v>
-      </c>
-      <c r="F178" s="5" t="s">
-        <v>719</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>720</v>
+        <v>934</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>937</v>
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:7">
-      <c r="A179" s="6"/>
+      <c r="A179" s="7"/>
       <c r="B179" s="2" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>934</v>
-      </c>
-      <c r="F179" s="5" t="s">
-        <v>935</v>
-      </c>
-      <c r="G179" s="5" t="s">
-        <v>936</v>
+        <v>940</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="G179" s="6" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="180" customHeight="1" spans="1:7">
-      <c r="A180" s="6"/>
+      <c r="A180" s="7"/>
       <c r="B180" s="2" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>722</v>
+        <v>945</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>724</v>
-      </c>
-      <c r="F180" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="G180" s="5" t="s">
-        <v>726</v>
+        <v>946</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="G180" s="6" t="s">
+        <v>948</v>
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:7">
-      <c r="A181" s="6"/>
+      <c r="A181" s="7"/>
       <c r="B181" s="2" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>939</v>
+        <v>730</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>941</v>
-      </c>
-      <c r="F181" s="5" t="s">
-        <v>942</v>
-      </c>
-      <c r="G181" s="5" t="s">
-        <v>943</v>
+        <v>731</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="G181" s="6" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:7">
-      <c r="A182" s="6"/>
+      <c r="A182" s="7"/>
       <c r="B182" s="2" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>945</v>
+        <v>736</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>947</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>948</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>949</v>
+        <v>737</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:7">
-      <c r="A183" s="6"/>
+      <c r="A183" s="7"/>
       <c r="B183" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="E183" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="F183" s="5" t="s">
+      <c r="E183" s="6" t="s">
         <v>954</v>
       </c>
-      <c r="G183" s="5" t="s">
+      <c r="F183" s="6" t="s">
         <v>955</v>
       </c>
+      <c r="G183" s="6" t="s">
+        <v>956</v>
+      </c>
     </row>
     <row r="184" customHeight="1" spans="1:7">
-      <c r="A184" s="6"/>
+      <c r="A184" s="7"/>
       <c r="B184" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>957</v>
+        <v>742</v>
       </c>
       <c r="D184" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="G184" s="6" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="1:7">
+      <c r="A185" s="7"/>
+      <c r="B185" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="E184" s="5" t="s">
+      <c r="C185" s="3" t="s">
         <v>959</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="D185" s="3" t="s">
         <v>960</v>
       </c>
-      <c r="G184" s="5" t="s">
+      <c r="E185" s="6" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="185" customHeight="1" spans="1:7">
-      <c r="A185" s="6"/>
-      <c r="B185" s="2" t="s">
+      <c r="F185" s="6" t="s">
         <v>962</v>
       </c>
-      <c r="C185" s="3" t="s">
+      <c r="G185" s="6" t="s">
         <v>963</v>
       </c>
-      <c r="D185" s="3" t="s">
+    </row>
+    <row r="186" customHeight="1" spans="1:7">
+      <c r="A186" s="7"/>
+      <c r="B186" s="2" t="s">
         <v>964</v>
       </c>
-      <c r="E185" s="5" t="s">
+      <c r="C186" s="3" t="s">
         <v>965</v>
       </c>
-      <c r="F185" s="5" t="s">
+      <c r="D186" s="3" t="s">
         <v>966</v>
       </c>
-      <c r="G185" s="5" t="s">
+      <c r="E186" s="6" t="s">
         <v>967</v>
       </c>
-    </row>
-    <row r="186" customHeight="1" spans="1:7">
-      <c r="A186" s="6"/>
-      <c r="B186" s="2" t="s">
+      <c r="F186" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="C186" s="3" t="s">
+      <c r="G186" s="6" t="s">
         <v>969</v>
       </c>
-      <c r="D186" s="3" t="s">
+    </row>
+    <row r="187" customHeight="1" spans="1:7">
+      <c r="A187" s="7"/>
+      <c r="B187" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="E186" s="3" t="s">
+      <c r="C187" s="3" t="s">
         <v>971</v>
       </c>
-      <c r="F186" s="3" t="s">
+      <c r="D187" s="3" t="s">
         <v>972</v>
       </c>
-      <c r="G186" s="3" t="s">
+      <c r="E187" s="6" t="s">
         <v>973</v>
       </c>
-    </row>
-    <row r="187" customHeight="1" spans="1:7">
-      <c r="A187" s="6"/>
-      <c r="B187" s="2" t="s">
+      <c r="F187" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="C187" s="3" t="s">
+      <c r="G187" s="6" t="s">
         <v>975</v>
       </c>
-      <c r="D187" s="3" t="s">
+    </row>
+    <row r="188" customHeight="1" spans="1:7">
+      <c r="A188" s="7"/>
+      <c r="B188" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="E187" s="3" t="s">
+      <c r="C188" s="3" t="s">
         <v>977</v>
       </c>
-      <c r="F187" s="3" t="s">
+      <c r="D188" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="G187" s="3" t="s">
+      <c r="E188" s="6" t="s">
         <v>979</v>
       </c>
-    </row>
-    <row r="188" customHeight="1" spans="1:7">
-      <c r="A188" s="6"/>
-      <c r="B188" s="2" t="s">
+      <c r="F188" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="C188" s="3" t="s">
+      <c r="G188" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="D188" s="3" t="s">
+    </row>
+    <row r="189" customHeight="1" spans="1:7">
+      <c r="A189" s="7"/>
+      <c r="B189" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="E188" s="3" t="s">
+      <c r="C189" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="F188" s="3" t="s">
+      <c r="D189" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="G188" s="3" t="s">
+      <c r="E189" s="6" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="189" customHeight="1" spans="1:7">
-      <c r="A189" s="6"/>
-      <c r="B189" s="2" t="s">
+      <c r="F189" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="C189" s="3" t="s">
+      <c r="G189" s="6" t="s">
         <v>987</v>
       </c>
-      <c r="D189" s="3" t="s">
+    </row>
+    <row r="190" customHeight="1" spans="1:7">
+      <c r="A190" s="7"/>
+      <c r="B190" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="E189" s="3" t="s">
+      <c r="C190" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="F189" s="3" t="s">
+      <c r="D190" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="G189" s="3" t="s">
+      <c r="E190" s="3" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="190" customHeight="1" spans="1:7">
-      <c r="A190" s="6"/>
-      <c r="B190" s="2" t="s">
+      <c r="F190" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="C190" s="3" t="s">
+      <c r="G190" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="D190" s="3" t="s">
+    </row>
+    <row r="191" customHeight="1" spans="1:7">
+      <c r="A191" s="7"/>
+      <c r="B191" s="2" t="s">
         <v>994</v>
       </c>
-      <c r="E190" s="3" t="s">
-        <v>994</v>
-      </c>
-      <c r="F190" s="3" t="s">
+      <c r="C191" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="G190" s="3" t="s">
+      <c r="D191" s="3" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="191" customHeight="1" spans="1:7">
-      <c r="A191" s="6"/>
-      <c r="B191" s="2" t="s">
+      <c r="E191" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="F191" s="3" t="s">
         <v>998</v>
       </c>
-      <c r="D191" s="3" t="s">
+      <c r="G191" s="3" t="s">
         <v>999</v>
       </c>
-      <c r="E191" s="3" t="s">
-        <v>999</v>
-      </c>
-      <c r="F191" s="3" t="s">
+    </row>
+    <row r="192" customHeight="1" spans="1:7">
+      <c r="A192" s="7"/>
+      <c r="B192" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="G191" s="3" t="s">
+      <c r="C192" s="3" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="192" customHeight="1" spans="1:7">
-      <c r="A192" s="6"/>
-      <c r="B192" s="2" t="s">
+      <c r="D192" s="3" t="s">
         <v>1002</v>
       </c>
-      <c r="C192" s="3" t="s">
+      <c r="E192" s="3" t="s">
         <v>1003</v>
       </c>
-      <c r="D192" s="3" t="s">
+      <c r="F192" s="3" t="s">
         <v>1004</v>
       </c>
-      <c r="E192" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F192" s="3" t="s">
+      <c r="G192" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="G192" s="3" t="s">
-        <v>1003</v>
-      </c>
     </row>
     <row r="193" customHeight="1" spans="1:7">
-      <c r="A193" s="6"/>
+      <c r="A193" s="7"/>
       <c r="B193" s="2" t="s">
         <v>1006</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>587</v>
+        <v>1007</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="G193" s="10" t="s">
-        <v>1009</v>
+        <v>1010</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>1011</v>
       </c>
     </row>
     <row r="194" customHeight="1" spans="1:7">
-      <c r="A194" s="2" t="s">
-        <v>704</v>
-      </c>
+      <c r="A194" s="7"/>
       <c r="B194" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E194" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="F194" s="2" t="s">
-        <v>707</v>
+      <c r="C194" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>1015</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>708</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="195" customHeight="1" spans="1:7">
-      <c r="A195" s="2"/>
+      <c r="A195" s="7"/>
       <c r="B195" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>367</v>
+        <v>1017</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>1020</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>368</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="196" customHeight="1" spans="1:7">
-      <c r="A196" s="2"/>
+      <c r="A196" s="7"/>
       <c r="B196" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>1018</v>
+        <v>1022</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>1025</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="197" customHeight="1" spans="1:7">
-      <c r="A197" s="2"/>
+      <c r="A197" s="7"/>
       <c r="B197" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>1024</v>
+        <v>1026</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="198" customHeight="1" spans="1:7">
-      <c r="A198" s="2"/>
+      <c r="A198" s="2" t="s">
+        <v>724</v>
+      </c>
       <c r="B198" s="2" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1026</v>
+        <v>724</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>1029</v>
+        <v>727</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>1030</v>
+        <v>728</v>
       </c>
     </row>
     <row r="199" customHeight="1" spans="1:7">
       <c r="A199" s="2"/>
       <c r="B199" s="2" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>1032</v>
+        <v>375</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>1033</v>
+        <v>376</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>1034</v>
+        <v>376</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>1035</v>
+        <v>377</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>1036</v>
+        <v>378</v>
       </c>
     </row>
     <row r="200" customHeight="1" spans="1:7">
       <c r="A200" s="2"/>
       <c r="B200" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E200" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="C200" s="2" t="s">
+      <c r="F200" s="2" t="s">
         <v>1038</v>
       </c>
-      <c r="D200" s="2" t="s">
+      <c r="G200" s="3" t="s">
         <v>1039</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:7">
       <c r="A201" s="2"/>
       <c r="B201" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F201" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="C201" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>1047</v>
-      </c>
       <c r="G201" s="3" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:7">
       <c r="A202" s="2"/>
       <c r="B202" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G202" s="3" t="s">
         <v>1049</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="1:7">
       <c r="A203" s="2"/>
       <c r="B203" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G203" s="3" t="s">
         <v>1055</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G203" s="3" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="204" customHeight="1" spans="1:7">
       <c r="A204" s="2"/>
       <c r="B204" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="C204" s="2" t="s">
+      <c r="G204" s="3" t="s">
         <v>1061</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="1:7">
       <c r="A205" s="2"/>
       <c r="B205" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F205" s="2" t="s">
         <v>1066</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>1067</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>1067</v>
@@ -8947,586 +9697,1552 @@
     <row r="206" customHeight="1" spans="1:7">
       <c r="A206" s="2"/>
       <c r="B206" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D206" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="C206" s="2" t="s">
+      <c r="E206" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="F206" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="E206" s="2" t="s">
+      <c r="G206" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="F206" s="2" t="s">
+    </row>
+    <row r="207" customHeight="1" spans="1:7">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2" t="s">
         <v>1074</v>
       </c>
-      <c r="G206" s="3" t="s">
+      <c r="C207" s="2" t="s">
         <v>1075</v>
       </c>
-    </row>
-    <row r="207" customHeight="1" spans="1:7">
-      <c r="A207" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="B207" s="3" t="s">
+      <c r="D207" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="E207" s="2" t="s">
         <v>1077</v>
       </c>
-      <c r="D207" s="3" t="s">
+      <c r="F207" s="2" t="s">
         <v>1078</v>
       </c>
-      <c r="E207" s="3" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>1080</v>
-      </c>
       <c r="G207" s="3" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="1:7">
       <c r="A208" s="2"/>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>1082</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="F208" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="D208" s="3" t="s">
+      <c r="G208" s="3" t="s">
         <v>1084</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G208" s="3" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:7">
       <c r="A209" s="2"/>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>1088</v>
       </c>
-      <c r="C209" s="3" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>1092</v>
+      <c r="F209" s="2" t="s">
+        <v>1086</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:7">
       <c r="A210" s="2"/>
       <c r="B210" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G210" s="3" t="s">
         <v>1094</v>
       </c>
-      <c r="C210" s="2" t="s">
+    </row>
+    <row r="211" customHeight="1" spans="1:7">
+      <c r="A211" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B211" s="3" t="s">
         <v>1095</v>
       </c>
-      <c r="D210" s="2" t="s">
+      <c r="C211" s="3" t="s">
         <v>1096</v>
       </c>
-      <c r="E210" s="2" t="s">
+      <c r="D211" s="3" t="s">
         <v>1097</v>
       </c>
-      <c r="F210" s="2" t="s">
+      <c r="E211" s="3" t="s">
         <v>1098</v>
       </c>
-      <c r="G210" s="3" t="s">
+      <c r="F211" s="3" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="211" customHeight="1" spans="1:7">
-      <c r="A211" s="2"/>
-      <c r="B211" s="2" t="s">
+      <c r="G211" s="3" t="s">
         <v>1100</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G211" s="3" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="212" customHeight="1" spans="1:7">
       <c r="A212" s="2"/>
-      <c r="B212" s="2" t="s">
+      <c r="B212" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G212" s="3" t="s">
         <v>1106</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="213" customHeight="1" spans="1:7">
       <c r="A213" s="2"/>
-      <c r="B213" s="2" t="s">
+      <c r="B213" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G213" s="3" t="s">
         <v>1112</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="214" customHeight="1" spans="1:7">
       <c r="A214" s="2"/>
       <c r="B214" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G214" s="3" t="s">
         <v>1118</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="215" customHeight="1" spans="1:7">
       <c r="A215" s="2"/>
       <c r="B215" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>1122</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="F215" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="D215" s="2" t="s">
+      <c r="G215" s="3" t="s">
         <v>1124</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>1126</v>
-      </c>
-      <c r="G215" s="3" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="216" customHeight="1" spans="1:7">
       <c r="A216" s="2"/>
       <c r="B216" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>1128</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="F216" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="G216" s="3" t="s">
         <v>1130</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:7">
       <c r="A217" s="2"/>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>1134</v>
       </c>
-      <c r="C217" s="2" t="s">
+      <c r="F217" s="2" t="s">
         <v>1135</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="G217" s="3" t="s">
         <v>1136</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>1138</v>
-      </c>
-      <c r="G217" s="3" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:7">
       <c r="A218" s="2"/>
       <c r="B218" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="C218" s="2" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>1143</v>
-      </c>
       <c r="F218" s="2" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:7">
       <c r="A219" s="2"/>
       <c r="B219" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G219" s="3" t="s">
         <v>1146</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G219" s="3" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:7">
       <c r="A220" s="2"/>
       <c r="B220" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G220" s="3" t="s">
         <v>1152</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>1156</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="221" customHeight="1" spans="1:7">
       <c r="A221" s="2"/>
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G221" s="3" t="s">
         <v>1158</v>
-      </c>
-      <c r="C221" s="3" t="s">
-        <v>1159</v>
-      </c>
-      <c r="D221" s="3" t="s">
-        <v>1160</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F221" s="3" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G221" s="3" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="222" customHeight="1" spans="1:7">
       <c r="A222" s="2"/>
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="C222" s="3" t="s">
+      <c r="G222" s="3" t="s">
         <v>1164</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>1167</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="223" customHeight="1" spans="1:7">
       <c r="A223" s="2"/>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F223" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="C223" s="3" t="s">
+      <c r="G223" s="3" t="s">
         <v>1170</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E223" s="3" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F223" s="3" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G223" s="3" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="224" customHeight="1" spans="1:7">
       <c r="A224" s="2"/>
       <c r="B224" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="G224" s="3" t="s">
         <v>1176</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>1177</v>
-      </c>
-      <c r="E224" s="5" t="s">
-        <v>1178</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>1179</v>
-      </c>
-      <c r="G224" s="5" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="225" customHeight="1" spans="1:7">
       <c r="A225" s="2"/>
       <c r="B225" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G225" s="3" t="s">
         <v>1181</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="G225" s="3" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="226" customHeight="1" spans="1:7">
       <c r="A226" s="2"/>
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E226" s="3" t="s">
         <v>1185</v>
       </c>
-      <c r="C226" s="2" t="s">
+      <c r="F226" s="3" t="s">
         <v>1186</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="G226" s="3" t="s">
         <v>1187</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="G226" s="3" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="227" customHeight="1" spans="1:7">
       <c r="A227" s="2"/>
-      <c r="B227" s="2" t="s">
+      <c r="B227" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D227" s="3" t="s">
         <v>1190</v>
       </c>
-      <c r="C227" s="2" t="s">
+      <c r="E227" s="3" t="s">
         <v>1191</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="F227" s="3" t="s">
         <v>1192</v>
       </c>
-      <c r="E227" s="2" t="s">
+      <c r="G227" s="3" t="s">
         <v>1193</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>1194</v>
-      </c>
-      <c r="G227" s="3" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="228" customHeight="1" spans="1:7">
       <c r="A228" s="2"/>
       <c r="B228" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>1196</v>
       </c>
-      <c r="C228" s="2" t="s">
+      <c r="E228" s="6" t="s">
         <v>1197</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="F228" s="6" t="s">
         <v>1198</v>
       </c>
-      <c r="E228" s="2" t="s">
+      <c r="G228" s="6" t="s">
         <v>1199</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>1200</v>
-      </c>
-      <c r="G228" s="3" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="229" customHeight="1" spans="1:7">
       <c r="A229" s="2"/>
       <c r="B229" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="C229" s="3" t="s">
+      <c r="E229" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F229" s="2" t="s">
         <v>1203</v>
       </c>
-      <c r="D229" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>1205</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G229" s="5" t="s">
-        <v>1207</v>
+      <c r="G229" s="3" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="230" customHeight="1" spans="1:7">
       <c r="A230" s="2"/>
       <c r="B230" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G230" s="3" t="s">
         <v>1208</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="G230" s="3" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="231" customHeight="1" spans="1:7">
       <c r="A231" s="2"/>
       <c r="B231" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G231" s="3" t="s">
         <v>1214</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>1216</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>1217</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G231" s="5" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="232" customHeight="1" spans="1:7">
       <c r="A232" s="2"/>
       <c r="B232" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G232" s="3" t="s">
         <v>1220</v>
       </c>
-      <c r="C232" s="2" t="s">
+    </row>
+    <row r="233" customHeight="1" spans="1:7">
+      <c r="A233" s="2"/>
+      <c r="B233" s="2" t="s">
         <v>1221</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="C233" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="E232" s="2" t="s">
+      <c r="D233" s="3" t="s">
         <v>1223</v>
       </c>
-      <c r="F232" s="2" t="s">
+      <c r="E233" s="6" t="s">
         <v>1224</v>
       </c>
-      <c r="G232" s="3" t="s">
+      <c r="F233" s="6" t="s">
         <v>1225</v>
+      </c>
+      <c r="G233" s="6" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="234" customHeight="1" spans="1:7">
+      <c r="A234" s="2"/>
+      <c r="B234" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="235" customHeight="1" spans="1:7">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F235" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G235" s="6" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="236" customHeight="1" spans="1:7">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="237" customHeight="1" spans="1:7">
+      <c r="A237" s="2"/>
+      <c r="B237" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="238" customHeight="1" spans="1:7">
+      <c r="A238" s="2"/>
+      <c r="B238" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="239" customHeight="1" spans="1:7">
+      <c r="A239" s="2"/>
+      <c r="B239" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="240" customHeight="1" spans="1:7">
+      <c r="A240" s="2"/>
+      <c r="B240" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="241" customHeight="1" spans="1:7">
+      <c r="A241" s="2"/>
+      <c r="B241" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="242" customHeight="1" spans="1:7">
+      <c r="A242" s="2"/>
+      <c r="B242" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="243" customHeight="1" spans="1:7">
+      <c r="A243" s="2"/>
+      <c r="B243" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="244" customHeight="1" spans="1:7">
+      <c r="A244" s="2"/>
+      <c r="B244" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="245" customHeight="1" spans="1:7">
+      <c r="A245" s="2"/>
+      <c r="B245" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="246" customHeight="1" spans="1:7">
+      <c r="A246" s="2"/>
+      <c r="B246" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="247" customHeight="1" spans="1:7">
+      <c r="A247" s="2"/>
+      <c r="B247" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="248" customHeight="1" spans="1:7">
+      <c r="A248" s="2"/>
+      <c r="B248" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="249" customHeight="1" spans="1:7">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="250" customHeight="1" spans="1:7">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="251" customHeight="1" spans="1:7">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="252" customHeight="1" spans="1:7">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="253" customHeight="1" spans="1:7">
+      <c r="A253" s="2"/>
+      <c r="B253" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="254" customHeight="1" spans="1:7">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="255" customHeight="1" spans="1:7">
+      <c r="A255" s="2"/>
+      <c r="B255" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="256" customHeight="1" spans="1:7">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="257" customHeight="1" spans="1:7">
+      <c r="A257" s="2"/>
+      <c r="B257" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="258" customHeight="1" spans="1:7">
+      <c r="A258" s="2"/>
+      <c r="B258" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="259" customHeight="1" spans="1:7">
+      <c r="A259" s="2"/>
+      <c r="B259" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="260" customHeight="1" spans="1:7">
+      <c r="A260" s="2"/>
+      <c r="B260" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="261" customHeight="1" spans="1:7">
+      <c r="A261" s="2"/>
+      <c r="B261" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F261" s="6" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G261" s="6" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="262" customHeight="1" spans="1:7">
+      <c r="A262" s="2"/>
+      <c r="B262" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="263" customHeight="1" spans="1:7">
+      <c r="A263" s="2"/>
+      <c r="B263" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="264" customHeight="1" spans="1:7">
+      <c r="A264" s="2"/>
+      <c r="B264" s="3" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="265" customHeight="1" spans="1:7">
+      <c r="A265" s="2"/>
+      <c r="B265" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="266" customHeight="1" spans="1:7">
+      <c r="A266" s="2"/>
+      <c r="B266" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="267" customHeight="1" spans="1:7">
+      <c r="A267" s="2"/>
+      <c r="B267" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="268" customHeight="1" spans="1:7">
+      <c r="A268" s="2"/>
+      <c r="B268" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="269" customHeight="1" spans="1:7">
+      <c r="A269" s="2"/>
+      <c r="B269" s="3" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="270" customHeight="1" spans="1:7">
+      <c r="A270" s="2"/>
+      <c r="B270" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="271" customHeight="1" spans="1:7">
+      <c r="A271" s="2"/>
+      <c r="B271" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="272" customHeight="1" spans="1:7">
+      <c r="A272" s="2"/>
+      <c r="B272" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F272" s="6" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G272" s="6" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="273" customHeight="1" spans="1:7">
+      <c r="A273" s="2"/>
+      <c r="B273" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="274" customHeight="1" spans="1:7">
+      <c r="A274" s="2"/>
+      <c r="B274" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="275" customHeight="1" spans="1:7">
+      <c r="A275" s="2"/>
+      <c r="B275" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="276" customHeight="1" spans="1:7">
+      <c r="A276" s="2"/>
+      <c r="B276" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="277" customHeight="1" spans="1:7">
+      <c r="A277" s="2"/>
+      <c r="B277" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="278" customHeight="1" spans="1:7">
+      <c r="A278" s="2"/>
+      <c r="B278" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F278" s="6" t="s">
+        <v>1474</v>
+      </c>
+      <c r="G278" s="6" t="s">
+        <v>1475</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A3:A16"/>
-    <mergeCell ref="A17:A33"/>
-    <mergeCell ref="A34:A66"/>
-    <mergeCell ref="A67:A75"/>
-    <mergeCell ref="A76:A88"/>
-    <mergeCell ref="A89:A93"/>
-    <mergeCell ref="A94:A104"/>
-    <mergeCell ref="A105:A123"/>
-    <mergeCell ref="A124:A133"/>
-    <mergeCell ref="A134:A193"/>
-    <mergeCell ref="A194:A206"/>
-    <mergeCell ref="A207:A232"/>
+    <mergeCell ref="A3:A18"/>
+    <mergeCell ref="A19:A35"/>
+    <mergeCell ref="A36:A68"/>
+    <mergeCell ref="A69:A78"/>
+    <mergeCell ref="A79:A91"/>
+    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="A97:A107"/>
+    <mergeCell ref="A108:A127"/>
+    <mergeCell ref="A128:A137"/>
+    <mergeCell ref="A138:A197"/>
+    <mergeCell ref="A198:A210"/>
+    <mergeCell ref="A211:A278"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/doc/usctranslations.xlsx
+++ b/doc/usctranslations.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="1476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="1497">
   <si>
     <t>Key</t>
   </si>
@@ -1274,6 +1274,24 @@
     <t>Hora de finalización</t>
   </si>
   <si>
+    <t>comm_picture</t>
+  </si>
+  <si>
+    <t>Picture</t>
+  </si>
+  <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <t>圖片</t>
+  </si>
+  <si>
+    <t>Imagem</t>
+  </si>
+  <si>
+    <t>Imagen</t>
+  </si>
+  <si>
     <t>comm_channel</t>
   </si>
   <si>
@@ -3560,6 +3578,54 @@
     <t>Configuración de reglas</t>
   </si>
   <si>
+    <t>ana_rule_type</t>
+  </si>
+  <si>
+    <t>Rule Type</t>
+  </si>
+  <si>
+    <t>规则类型</t>
+  </si>
+  <si>
+    <t>規則類型</t>
+  </si>
+  <si>
+    <t>Tipo de Regra</t>
+  </si>
+  <si>
+    <t>Tipo de regla</t>
+  </si>
+  <si>
+    <t>ana_goal</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>目標</t>
+  </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>ana_event</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>Eventos</t>
+  </si>
+  <si>
     <t>ana_event_search</t>
   </si>
   <si>
@@ -4335,9 +4401,6 @@
   </si>
   <si>
     <t>Tipo de regra</t>
-  </si>
-  <si>
-    <t>Tipo de regla</t>
   </si>
   <si>
     <t>ana_fps</t>
@@ -5493,7 +5556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G278"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="31.95" customHeight="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.775" style="1" customWidth="1"/>
@@ -7102,31 +7165,31 @@
         <v>417</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:7">
       <c r="A77" s="7"/>
       <c r="B77" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>424</v>
@@ -7137,105 +7200,105 @@
       <c r="B78" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" s="3" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:7">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="7"/>
+      <c r="B79" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="E79" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:7">
+      <c r="A80" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="E80" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F79" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="G79" s="6" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="1:7">
-      <c r="A80" s="7"/>
-      <c r="B80" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>231</v>
+      <c r="F80" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:7">
       <c r="A81" s="7"/>
       <c r="B81" s="2" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>438</v>
+        <v>228</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>439</v>
+        <v>229</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>439</v>
+        <v>229</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>440</v>
+        <v>230</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>441</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:7">
       <c r="A82" s="7"/>
       <c r="B82" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="E82" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="E82" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F82" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" s="3" t="s">
         <v>447</v>
       </c>
     </row>
@@ -7251,33 +7314,33 @@
         <v>450</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:7">
       <c r="A84" s="7"/>
       <c r="B84" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="G84" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="G84" s="10" t="s">
         <v>457</v>
       </c>
     </row>
@@ -7409,50 +7472,50 @@
     </row>
     <row r="91" customHeight="1" spans="1:7">
       <c r="A91" s="7"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
+      <c r="B91" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="92" customHeight="1" spans="1:7">
-      <c r="A92" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>499</v>
-      </c>
+      <c r="A92" s="7"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" customHeight="1" spans="1:7">
-      <c r="A93" s="7"/>
+      <c r="A93" s="7" t="s">
+        <v>500</v>
+      </c>
       <c r="B93" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>505</v>
@@ -7470,25 +7533,25 @@
         <v>508</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="G94" s="5" t="s">
         <v>510</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:7">
       <c r="A95" s="7"/>
       <c r="B95" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>514</v>
@@ -7522,46 +7585,46 @@
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:7">
-      <c r="A97" s="7" t="s">
-        <v>433</v>
-      </c>
+      <c r="A97" s="7"/>
       <c r="B97" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E97" s="2" t="s">
+      <c r="E97" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="F97" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="G97" s="5" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:7">
-      <c r="A98" s="7"/>
-      <c r="B98" s="3" t="s">
+      <c r="A98" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="E98" s="6" t="s">
+      <c r="E98" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="F98" s="6" t="s">
+      <c r="F98" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="G98" s="6" t="s">
+      <c r="G98" s="3" t="s">
         <v>534</v>
       </c>
     </row>
@@ -7630,27 +7693,45 @@
     </row>
     <row r="102" customHeight="1" spans="1:7">
       <c r="A102" s="7"/>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="D102" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E102" s="2" t="s">
+      <c r="E102" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="F102" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="G102" s="6" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:7">
       <c r="A103" s="7"/>
+      <c r="B103" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="104" customHeight="1" spans="1:7">
       <c r="A104" s="7"/>
@@ -7665,30 +7746,12 @@
       <c r="A107" s="7"/>
     </row>
     <row r="108" customHeight="1" spans="1:7">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="7"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:7">
+      <c r="A109" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>562</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>563</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="109" customHeight="1" spans="1:7">
-      <c r="A109" s="7"/>
       <c r="B109" s="2" t="s">
         <v>565</v>
       </c>
@@ -7710,7 +7773,7 @@
     </row>
     <row r="110" customHeight="1" spans="1:7">
       <c r="A110" s="7"/>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>571</v>
       </c>
       <c r="C110" s="3" t="s">
@@ -7782,19 +7845,19 @@
       <c r="D113" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="G113" s="6" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:7">
       <c r="A114" s="7"/>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="3" t="s">
         <v>595</v>
       </c>
       <c r="C114" s="3" t="s">
@@ -7804,25 +7867,25 @@
         <v>597</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="G114" s="5" t="s">
         <v>599</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:7">
       <c r="A115" s="7"/>
       <c r="B115" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>603</v>
@@ -7830,7 +7893,7 @@
       <c r="F115" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G115" s="5" t="s">
         <v>605</v>
       </c>
     </row>
@@ -7852,70 +7915,70 @@
         <v>610</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:7">
       <c r="A117" s="7"/>
-      <c r="B117" s="3" t="s">
-        <v>611</v>
+      <c r="B117" s="2" t="s">
+        <v>612</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="E117" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="F117" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="G117" s="6" t="s">
+      <c r="E117" s="3" t="s">
         <v>615</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:7">
       <c r="A118" s="7"/>
-      <c r="B118" s="2" t="s">
-        <v>616</v>
+      <c r="B118" s="3" t="s">
+        <v>617</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:7">
       <c r="A119" s="7"/>
-      <c r="B119" s="3" t="s">
-        <v>618</v>
+      <c r="B119" s="2" t="s">
+        <v>622</v>
       </c>
       <c r="C119" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="E119" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="E119" s="6" t="s">
+      <c r="F119" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="F119" s="6" t="s">
-        <v>622</v>
-      </c>
       <c r="G119" s="6" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:7">
@@ -8035,62 +8098,62 @@
         <v>656</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:7">
       <c r="A126" s="7"/>
+      <c r="B126" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="127" customHeight="1" spans="1:7">
       <c r="A127" s="7"/>
     </row>
     <row r="128" customHeight="1" spans="1:7">
-      <c r="A128" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="G128" s="3" t="s">
-        <v>664</v>
-      </c>
+      <c r="A128" s="7"/>
     </row>
     <row r="129" customHeight="1" spans="1:7">
-      <c r="A129" s="7"/>
-      <c r="B129" s="3" t="s">
+      <c r="A129" s="7" t="s">
         <v>665</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="C129" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D129" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E129" s="6" t="s">
+      <c r="E129" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F129" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="G129" s="3" t="s">
         <v>670</v>
       </c>
     </row>
@@ -8112,27 +8175,27 @@
         <v>675</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:7">
       <c r="A131" s="7"/>
       <c r="B131" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="E131" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="E131" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="F131" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="G131" s="6" t="s">
         <v>681</v>
       </c>
     </row>
@@ -8148,25 +8211,25 @@
         <v>684</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:7">
       <c r="A133" s="7"/>
       <c r="B133" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>690</v>
@@ -8175,61 +8238,61 @@
         <v>691</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:7">
       <c r="A134" s="7"/>
       <c r="B134" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="E134" s="6" t="s">
         <v>695</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="E134" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="G134" s="6" t="s">
-        <v>693</v>
+      <c r="F134" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:7">
       <c r="A135" s="7"/>
       <c r="B135" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D135" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="G135" s="6" t="s">
         <v>699</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>700</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:7">
       <c r="A136" s="7"/>
       <c r="B136" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>705</v>
@@ -8263,73 +8326,73 @@
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:7">
-      <c r="A138" s="7" t="s">
+      <c r="A138" s="7"/>
+      <c r="B138" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="C138" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>714</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="F138" s="6" t="s">
         <v>718</v>
       </c>
-      <c r="G138" s="3" t="s">
-        <v>718</v>
+      <c r="G138" s="6" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:7">
-      <c r="A139" s="7"/>
+      <c r="A139" s="7" t="s">
+        <v>720</v>
+      </c>
       <c r="B139" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>102</v>
+        <v>720</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>721</v>
-      </c>
-      <c r="F139" s="6" t="s">
         <v>722</v>
       </c>
-      <c r="G139" s="6" t="s">
-        <v>231</v>
+      <c r="E139" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:7">
       <c r="A140" s="7"/>
       <c r="B140" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>724</v>
+        <v>102</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="E140" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="E140" s="6" t="s">
         <v>727</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="F140" s="6" t="s">
         <v>728</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="1:7">
       <c r="A141" s="7"/>
-      <c r="B141" s="6" t="s">
+      <c r="B141" s="3" t="s">
         <v>729</v>
       </c>
       <c r="C141" s="3" t="s">
@@ -8338,13 +8401,13 @@
       <c r="D141" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="E141" s="6" t="s">
+      <c r="E141" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="F141" s="6" t="s">
+      <c r="F141" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="G141" s="6" t="s">
+      <c r="G141" s="3" t="s">
         <v>734</v>
       </c>
     </row>
@@ -8392,22 +8455,22 @@
     </row>
     <row r="144" customHeight="1" spans="1:7">
       <c r="A144" s="7"/>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="C144" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="D144" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="E144" s="6" t="s">
         <v>750</v>
       </c>
-      <c r="F144" s="2" t="s">
+      <c r="F144" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="6" t="s">
         <v>752</v>
       </c>
     </row>
@@ -8450,108 +8513,108 @@
         <v>763</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:7">
       <c r="A147" s="7"/>
       <c r="B147" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>596</v>
+        <v>766</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>599</v>
+        <v>769</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:7">
       <c r="A148" s="7"/>
-      <c r="B148" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="E148" s="6" t="s">
+      <c r="B148" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="F148" s="6" t="s">
+      <c r="C148" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D148" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="E148" s="2" t="s">
         <v>772</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="1:7">
       <c r="A149" s="7"/>
-      <c r="B149" s="6" t="s">
+      <c r="B149" s="3" t="s">
         <v>773</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>742</v>
+        <v>774</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>743</v>
+        <v>775</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>744</v>
+        <v>776</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>745</v>
+        <v>777</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>746</v>
+        <v>778</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:7">
       <c r="A150" s="7"/>
-      <c r="B150" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="G150" s="3" t="s">
+      <c r="B150" s="6" t="s">
         <v>779</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:7">
       <c r="A151" s="7"/>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="C151" s="3" t="s">
+      <c r="C151" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="D151" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="E151" s="3" t="s">
+      <c r="E151" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="F151" s="3" t="s">
+      <c r="F151" s="2" t="s">
         <v>784</v>
       </c>
       <c r="G151" s="3" t="s">
@@ -8560,19 +8623,19 @@
     </row>
     <row r="152" customHeight="1" spans="1:7">
       <c r="A152" s="7"/>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="C152" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="D152" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="E152" s="2" t="s">
+      <c r="E152" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="F152" s="3" t="s">
         <v>790</v>
       </c>
       <c r="G152" s="3" t="s">
@@ -8581,56 +8644,56 @@
     </row>
     <row r="153" customHeight="1" spans="1:7">
       <c r="A153" s="7"/>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C153" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="E153" s="6" t="s">
+      <c r="E153" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="F153" s="6" t="s">
+      <c r="F153" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="G153" s="6" t="s">
+      <c r="G153" s="3" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:7">
       <c r="A154" s="7"/>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="C154" s="2" t="s">
+      <c r="C154" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="D154" s="2" t="s">
+      <c r="D154" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="E154" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="F154" s="2" t="s">
+      <c r="E154" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="G154" s="3" t="s">
+      <c r="F154" s="6" t="s">
         <v>802</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:7">
       <c r="A155" s="7"/>
       <c r="B155" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>806</v>
@@ -8638,7 +8701,7 @@
       <c r="F155" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="G155" s="5" t="s">
+      <c r="G155" s="3" t="s">
         <v>808</v>
       </c>
     </row>
@@ -8659,7 +8722,7 @@
       <c r="F156" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="G156" s="3" t="s">
+      <c r="G156" s="5" t="s">
         <v>814</v>
       </c>
     </row>
@@ -8674,13 +8737,13 @@
       <c r="D157" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="E157" s="11" t="s">
+      <c r="E157" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="F157" s="11" t="s">
+      <c r="F157" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="G157" s="6" t="s">
+      <c r="G157" s="3" t="s">
         <v>820</v>
       </c>
     </row>
@@ -8689,16 +8752,16 @@
       <c r="B158" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="E158" s="6" t="s">
+      <c r="E158" s="11" t="s">
         <v>824</v>
       </c>
-      <c r="F158" s="6" t="s">
+      <c r="F158" s="11" t="s">
         <v>825</v>
       </c>
       <c r="G158" s="6" t="s">
@@ -8710,38 +8773,38 @@
       <c r="B159" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D159" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="E159" s="2" t="s">
+      <c r="E159" s="6" t="s">
         <v>830</v>
       </c>
-      <c r="F159" s="2" t="s">
+      <c r="F159" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>831</v>
+      <c r="G159" s="6" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="160" customHeight="1" spans="1:7">
       <c r="A160" s="7"/>
       <c r="B160" s="2" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>837</v>
@@ -8752,59 +8815,59 @@
       <c r="B161" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="D161" s="3" t="s">
+      <c r="D161" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="E161" s="3" t="s">
+      <c r="E161" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="F161" s="3" t="s">
+      <c r="F161" s="2" t="s">
         <v>842</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="162" customHeight="1" spans="1:7">
       <c r="A162" s="7"/>
       <c r="B162" s="2" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>309</v>
+        <v>848</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="163" customHeight="1" spans="1:7">
       <c r="A163" s="7"/>
       <c r="B163" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>852</v>
+        <v>309</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>853</v>
@@ -8905,13 +8968,13 @@
       <c r="D168" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="E168" s="6" t="s">
+      <c r="E168" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="F168" s="6" t="s">
+      <c r="F168" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="G168" s="6" t="s">
+      <c r="G168" s="3" t="s">
         <v>883</v>
       </c>
     </row>
@@ -8989,13 +9052,13 @@
       <c r="D172" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="E172" s="3" t="s">
+      <c r="E172" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="F172" s="3" t="s">
+      <c r="F172" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="G172" s="3" t="s">
+      <c r="G172" s="6" t="s">
         <v>907</v>
       </c>
     </row>
@@ -9010,13 +9073,13 @@
       <c r="D173" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="E173" s="6" t="s">
+      <c r="E173" s="3" t="s">
         <v>911</v>
       </c>
-      <c r="F173" s="6" t="s">
+      <c r="F173" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="G173" s="6" t="s">
+      <c r="G173" s="3" t="s">
         <v>913</v>
       </c>
     </row>
@@ -9086,43 +9149,43 @@
     <row r="177" customHeight="1" spans="1:7">
       <c r="A177" s="7"/>
       <c r="B177" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="G177" s="3" t="s">
-        <v>791</v>
+        <v>932</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>937</v>
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:7">
       <c r="A178" s="7"/>
       <c r="B178" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="E178" s="6" t="s">
-        <v>935</v>
-      </c>
-      <c r="F178" s="6" t="s">
-        <v>936</v>
-      </c>
-      <c r="G178" s="6" t="s">
-        <v>937</v>
+        <v>792</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:7">
@@ -9158,40 +9221,40 @@
         <v>946</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>732</v>
+        <v>947</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:7">
       <c r="A181" s="7"/>
       <c r="B181" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>730</v>
+        <v>951</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>731</v>
+        <v>952</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>733</v>
+        <v>953</v>
       </c>
       <c r="G181" s="6" t="s">
-        <v>734</v>
+        <v>954</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:7">
       <c r="A182" s="7"/>
       <c r="B182" s="2" t="s">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>736</v>
@@ -9212,22 +9275,22 @@
     <row r="183" customHeight="1" spans="1:7">
       <c r="A183" s="7"/>
       <c r="B183" s="2" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>952</v>
+        <v>742</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>953</v>
+        <v>743</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>954</v>
+        <v>744</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>955</v>
+        <v>745</v>
       </c>
       <c r="G183" s="6" t="s">
-        <v>956</v>
+        <v>746</v>
       </c>
     </row>
     <row r="184" customHeight="1" spans="1:7">
@@ -9236,40 +9299,40 @@
         <v>957</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>742</v>
+        <v>958</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>743</v>
+        <v>959</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>744</v>
+        <v>960</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>745</v>
+        <v>961</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>746</v>
+        <v>962</v>
       </c>
     </row>
     <row r="185" customHeight="1" spans="1:7">
       <c r="A185" s="7"/>
       <c r="B185" s="2" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>959</v>
+        <v>748</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>960</v>
+        <v>749</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>961</v>
+        <v>750</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>962</v>
+        <v>751</v>
       </c>
       <c r="G185" s="6" t="s">
-        <v>963</v>
+        <v>752</v>
       </c>
     </row>
     <row r="186" customHeight="1" spans="1:7">
@@ -9367,13 +9430,13 @@
       <c r="D190" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="E190" s="3" t="s">
+      <c r="E190" s="6" t="s">
         <v>991</v>
       </c>
-      <c r="F190" s="3" t="s">
+      <c r="F190" s="6" t="s">
         <v>992</v>
       </c>
-      <c r="G190" s="3" t="s">
+      <c r="G190" s="6" t="s">
         <v>993</v>
       </c>
     </row>
@@ -9452,141 +9515,141 @@
         <v>1014</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="195" customHeight="1" spans="1:7">
       <c r="A195" s="7"/>
       <c r="B195" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="196" customHeight="1" spans="1:7">
       <c r="A196" s="7"/>
       <c r="B196" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="197" customHeight="1" spans="1:7">
       <c r="A197" s="7"/>
       <c r="B197" s="2" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>601</v>
+        <v>1029</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G197" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G197" s="3" t="s">
         <v>1029</v>
       </c>
     </row>
     <row r="198" customHeight="1" spans="1:7">
-      <c r="A198" s="2" t="s">
-        <v>724</v>
-      </c>
+      <c r="A198" s="7"/>
       <c r="B198" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E198" s="2" t="s">
         <v>1032</v>
       </c>
-      <c r="F198" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="G198" s="3" t="s">
-        <v>728</v>
+      <c r="C198" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G198" s="5" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="199" customHeight="1" spans="1:7">
-      <c r="A199" s="2"/>
+      <c r="A199" s="2" t="s">
+        <v>730</v>
+      </c>
       <c r="B199" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>375</v>
+        <v>730</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>376</v>
+        <v>1037</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>376</v>
+        <v>1038</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>377</v>
+        <v>733</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>378</v>
+        <v>734</v>
       </c>
     </row>
     <row r="200" customHeight="1" spans="1:7">
       <c r="A200" s="2"/>
       <c r="B200" s="2" t="s">
-        <v>1034</v>
+        <v>1039</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>1035</v>
+        <v>375</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1036</v>
+        <v>376</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>1037</v>
+        <v>376</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>1038</v>
+        <v>377</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>1039</v>
+        <v>378</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:7">
@@ -9595,37 +9658,37 @@
         <v>1040</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>416</v>
+        <v>1041</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:7">
       <c r="A202" s="2"/>
       <c r="B202" s="2" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>1045</v>
+        <v>422</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>1049</v>
@@ -9733,25 +9796,25 @@
         <v>1078</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="208" customHeight="1" spans="1:7">
       <c r="A208" s="2"/>
       <c r="B208" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>1084</v>
@@ -9772,50 +9835,48 @@
         <v>1088</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:7">
       <c r="A210" s="2"/>
       <c r="B210" s="2" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="E210" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F210" s="2" t="s">
         <v>1092</v>
       </c>
-      <c r="F210" s="2" t="s">
-        <v>1093</v>
-      </c>
       <c r="G210" s="3" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="211" customHeight="1" spans="1:7">
-      <c r="A211" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B211" s="3" t="s">
+      <c r="A211" s="2"/>
+      <c r="B211" s="2" t="s">
         <v>1095</v>
       </c>
-      <c r="C211" s="3" t="s">
+      <c r="C211" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="D211" s="3" t="s">
+      <c r="D211" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="E211" s="3" t="s">
+      <c r="E211" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="F211" s="3" t="s">
+      <c r="F211" s="2" t="s">
         <v>1099</v>
       </c>
       <c r="G211" s="3" t="s">
@@ -9823,7 +9884,9 @@
       </c>
     </row>
     <row r="212" customHeight="1" spans="1:7">
-      <c r="A212" s="2"/>
+      <c r="A212" s="2" t="s">
+        <v>444</v>
+      </c>
       <c r="B212" s="3" t="s">
         <v>1101</v>
       </c>
@@ -9866,19 +9929,19 @@
     </row>
     <row r="214" customHeight="1" spans="1:7">
       <c r="A214" s="2"/>
-      <c r="B214" s="2" t="s">
+      <c r="B214" s="3" t="s">
         <v>1113</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="C214" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="D214" s="2" t="s">
+      <c r="D214" s="3" t="s">
         <v>1115</v>
       </c>
-      <c r="E214" s="2" t="s">
+      <c r="E214" s="3" t="s">
         <v>1116</v>
       </c>
-      <c r="F214" s="2" t="s">
+      <c r="F214" s="3" t="s">
         <v>1117</v>
       </c>
       <c r="G214" s="3" t="s">
@@ -9963,31 +10026,31 @@
         <v>1140</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:7">
       <c r="A219" s="2"/>
       <c r="B219" s="2" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="E219" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>1144</v>
       </c>
-      <c r="F219" s="2" t="s">
-        <v>1145</v>
-      </c>
       <c r="G219" s="3" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:7">
@@ -10013,7 +10076,7 @@
     </row>
     <row r="221" customHeight="1" spans="1:7">
       <c r="A221" s="2"/>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="2" t="s">
         <v>1153</v>
       </c>
       <c r="C221" s="2" t="s">
@@ -10034,7 +10097,7 @@
     </row>
     <row r="222" customHeight="1" spans="1:7">
       <c r="A222" s="2"/>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="3" t="s">
         <v>1159</v>
       </c>
       <c r="C222" s="2" t="s">
@@ -10100,101 +10163,101 @@
       <c r="B225" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="C225" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="D225" s="3" t="s">
+      <c r="D225" s="2" t="s">
         <v>1179</v>
       </c>
-      <c r="E225" s="3" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F225" s="3" t="s">
+      <c r="E225" s="2" t="s">
         <v>1180</v>
       </c>
+      <c r="F225" s="2" t="s">
+        <v>1181</v>
+      </c>
       <c r="G225" s="3" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="226" customHeight="1" spans="1:7">
       <c r="A226" s="2"/>
-      <c r="B226" s="3" t="s">
-        <v>1182</v>
+      <c r="B226" s="2" t="s">
+        <v>1183</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="227" customHeight="1" spans="1:7">
       <c r="A227" s="2"/>
-      <c r="B227" s="3" t="s">
-        <v>1188</v>
+      <c r="B227" s="2" t="s">
+        <v>1189</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="228" customHeight="1" spans="1:7">
       <c r="A228" s="2"/>
       <c r="B228" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>1196</v>
-      </c>
-      <c r="E228" s="6" t="s">
         <v>1197</v>
       </c>
-      <c r="F228" s="6" t="s">
+      <c r="E228" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F228" s="3" t="s">
         <v>1198</v>
       </c>
-      <c r="G228" s="6" t="s">
-        <v>1199</v>
+      <c r="G228" s="3" t="s">
+        <v>1198</v>
       </c>
     </row>
     <row r="229" customHeight="1" spans="1:7">
       <c r="A229" s="2"/>
       <c r="B229" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C229" s="3" t="s">
         <v>1200</v>
       </c>
-      <c r="C229" s="2" t="s">
+      <c r="D229" s="3" t="s">
         <v>1201</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="E229" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F229" s="3" t="s">
         <v>1202</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>1203</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>1203</v>
@@ -10202,350 +10265,350 @@
     </row>
     <row r="230" customHeight="1" spans="1:7">
       <c r="A230" s="2"/>
-      <c r="B230" s="2" t="s">
+      <c r="B230" s="3" t="s">
         <v>1204</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C230" s="3" t="s">
         <v>1205</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="D230" s="3" t="s">
         <v>1206</v>
       </c>
-      <c r="E230" s="2" t="s">
-        <v>1206</v>
-      </c>
-      <c r="F230" s="2" t="s">
+      <c r="E230" s="3" t="s">
         <v>1207</v>
       </c>
+      <c r="F230" s="3" t="s">
+        <v>1208</v>
+      </c>
       <c r="G230" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="231" customHeight="1" spans="1:7">
       <c r="A231" s="2"/>
-      <c r="B231" s="2" t="s">
-        <v>1209</v>
-      </c>
-      <c r="C231" s="2" t="s">
+      <c r="B231" s="3" t="s">
         <v>1210</v>
       </c>
-      <c r="D231" s="2" t="s">
+      <c r="C231" s="3" t="s">
         <v>1211</v>
       </c>
-      <c r="E231" s="2" t="s">
+      <c r="D231" s="3" t="s">
         <v>1212</v>
       </c>
-      <c r="F231" s="2" t="s">
+      <c r="E231" s="3" t="s">
         <v>1213</v>
       </c>
+      <c r="F231" s="3" t="s">
+        <v>1214</v>
+      </c>
       <c r="G231" s="3" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="232" customHeight="1" spans="1:7">
       <c r="A232" s="2"/>
       <c r="B232" s="2" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C232" s="2" t="s">
         <v>1216</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="C232" s="3" t="s">
         <v>1217</v>
       </c>
-      <c r="E232" s="2" t="s">
+      <c r="D232" s="3" t="s">
         <v>1218</v>
       </c>
-      <c r="F232" s="2" t="s">
+      <c r="E232" s="6" t="s">
         <v>1219</v>
       </c>
-      <c r="G232" s="3" t="s">
+      <c r="F232" s="6" t="s">
         <v>1220</v>
+      </c>
+      <c r="G232" s="6" t="s">
+        <v>1221</v>
       </c>
     </row>
     <row r="233" customHeight="1" spans="1:7">
       <c r="A233" s="2"/>
       <c r="B233" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C233" s="3" t="s">
         <v>1222</v>
       </c>
-      <c r="D233" s="3" t="s">
+      <c r="C233" s="2" t="s">
         <v>1223</v>
       </c>
-      <c r="E233" s="6" t="s">
+      <c r="D233" s="2" t="s">
         <v>1224</v>
       </c>
-      <c r="F233" s="6" t="s">
+      <c r="E233" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>1225</v>
       </c>
-      <c r="G233" s="6" t="s">
-        <v>1226</v>
+      <c r="G233" s="3" t="s">
+        <v>1225</v>
       </c>
     </row>
     <row r="234" customHeight="1" spans="1:7">
       <c r="A234" s="2"/>
       <c r="B234" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>1227</v>
       </c>
-      <c r="C234" s="2" t="s">
+      <c r="D234" s="2" t="s">
         <v>1228</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="E234" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>1229</v>
       </c>
-      <c r="E234" s="2" t="s">
+      <c r="G234" s="3" t="s">
         <v>1230</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="235" customHeight="1" spans="1:7">
       <c r="A235" s="2"/>
       <c r="B235" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D235" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="C235" s="3" t="s">
+      <c r="E235" s="2" t="s">
         <v>1234</v>
       </c>
-      <c r="D235" s="3" t="s">
+      <c r="F235" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="E235" s="6" t="s">
+      <c r="G235" s="3" t="s">
         <v>1236</v>
-      </c>
-      <c r="F235" s="6" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G235" s="6" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="236" customHeight="1" spans="1:7">
       <c r="A236" s="2"/>
       <c r="B236" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D236" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="C236" s="2" t="s">
+      <c r="E236" s="2" t="s">
         <v>1240</v>
       </c>
-      <c r="D236" s="2" t="s">
+      <c r="F236" s="2" t="s">
         <v>1241</v>
       </c>
-      <c r="E236" s="2" t="s">
+      <c r="G236" s="3" t="s">
         <v>1242</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>1243</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="237" customHeight="1" spans="1:7">
       <c r="A237" s="2"/>
-      <c r="B237" s="3" t="s">
+      <c r="B237" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D237" s="3" t="s">
         <v>1245</v>
       </c>
-      <c r="C237" s="3" t="s">
+      <c r="E237" s="6" t="s">
         <v>1246</v>
       </c>
-      <c r="D237" s="3" t="s">
+      <c r="F237" s="6" t="s">
         <v>1247</v>
       </c>
-      <c r="E237" s="3" t="s">
+      <c r="G237" s="6" t="s">
         <v>1248</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="238" customHeight="1" spans="1:7">
       <c r="A238" s="2"/>
-      <c r="B238" s="3" t="s">
+      <c r="B238" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D238" s="2" t="s">
         <v>1251</v>
       </c>
-      <c r="C238" s="3" t="s">
+      <c r="E238" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="D238" s="3" t="s">
+      <c r="F238" s="2" t="s">
         <v>1253</v>
       </c>
-      <c r="E238" s="3" t="s">
-        <v>1253</v>
-      </c>
-      <c r="F238" s="3" t="s">
+      <c r="G238" s="3" t="s">
         <v>1254</v>
-      </c>
-      <c r="G238" s="3" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="239" customHeight="1" spans="1:7">
       <c r="A239" s="2"/>
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C239" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="C239" s="3" t="s">
+      <c r="D239" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="D239" s="3" t="s">
+      <c r="E239" s="6" t="s">
         <v>1258</v>
       </c>
-      <c r="E239" s="3" t="s">
-        <v>1258</v>
-      </c>
-      <c r="F239" s="3" t="s">
+      <c r="F239" s="6" t="s">
         <v>1259</v>
       </c>
-      <c r="G239" s="3" t="s">
+      <c r="G239" s="6" t="s">
         <v>1260</v>
       </c>
     </row>
     <row r="240" customHeight="1" spans="1:7">
       <c r="A240" s="2"/>
-      <c r="B240" s="3" t="s">
+      <c r="B240" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="C240" s="3" t="s">
+      <c r="C240" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="D240" s="3" t="s">
+      <c r="D240" s="2" t="s">
         <v>1263</v>
       </c>
-      <c r="E240" s="3" t="s">
-        <v>1263</v>
-      </c>
-      <c r="F240" s="3" t="s">
+      <c r="E240" s="2" t="s">
         <v>1264</v>
       </c>
+      <c r="F240" s="2" t="s">
+        <v>1265</v>
+      </c>
       <c r="G240" s="3" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="241" customHeight="1" spans="1:7">
       <c r="A241" s="2"/>
       <c r="B241" s="3" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="242" customHeight="1" spans="1:7">
       <c r="A242" s="2"/>
       <c r="B242" s="3" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="243" customHeight="1" spans="1:7">
       <c r="A243" s="2"/>
       <c r="B243" s="3" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="244" customHeight="1" spans="1:7">
       <c r="A244" s="2"/>
       <c r="B244" s="3" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="245" customHeight="1" spans="1:7">
       <c r="A245" s="2"/>
       <c r="B245" s="3" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="246" customHeight="1" spans="1:7">
       <c r="A246" s="2"/>
       <c r="B246" s="3" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>1295</v>
@@ -10569,73 +10632,73 @@
         <v>1300</v>
       </c>
       <c r="E247" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F247" s="3" t="s">
         <v>1301</v>
       </c>
-      <c r="F247" s="3" t="s">
+      <c r="G247" s="3" t="s">
         <v>1302</v>
-      </c>
-      <c r="G247" s="3" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="248" customHeight="1" spans="1:7">
       <c r="A248" s="2"/>
       <c r="B248" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C248" s="3" t="s">
         <v>1304</v>
       </c>
-      <c r="C248" s="3" t="s">
+      <c r="D248" s="3" t="s">
         <v>1305</v>
       </c>
-      <c r="D248" s="3" t="s">
+      <c r="E248" s="3" t="s">
         <v>1306</v>
       </c>
-      <c r="E248" s="3" t="s">
+      <c r="F248" s="3" t="s">
         <v>1307</v>
       </c>
-      <c r="F248" s="3" t="s">
-        <v>1308</v>
-      </c>
       <c r="G248" s="3" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="249" customHeight="1" spans="1:7">
       <c r="A249" s="2"/>
-      <c r="B249" s="2" t="s">
+      <c r="B249" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C249" s="3" t="s">
         <v>1309</v>
       </c>
-      <c r="C249" s="2" t="s">
+      <c r="D249" s="3" t="s">
         <v>1310</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="E249" s="3" t="s">
         <v>1311</v>
       </c>
-      <c r="E249" s="2" t="s">
+      <c r="F249" s="3" t="s">
         <v>1312</v>
       </c>
-      <c r="F249" s="2" t="s">
+      <c r="G249" s="3" t="s">
         <v>1313</v>
-      </c>
-      <c r="G249" s="3" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="250" customHeight="1" spans="1:7">
       <c r="A250" s="2"/>
-      <c r="B250" s="2" t="s">
+      <c r="B250" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C250" s="3" t="s">
         <v>1315</v>
       </c>
-      <c r="C250" s="2" t="s">
+      <c r="D250" s="3" t="s">
         <v>1316</v>
       </c>
-      <c r="D250" s="2" t="s">
+      <c r="E250" s="3" t="s">
         <v>1317</v>
       </c>
-      <c r="E250" s="2" t="s">
+      <c r="F250" s="3" t="s">
         <v>1318</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>1319</v>
       </c>
       <c r="G250" s="3" t="s">
         <v>1319</v>
@@ -10643,19 +10706,19 @@
     </row>
     <row r="251" customHeight="1" spans="1:7">
       <c r="A251" s="2"/>
-      <c r="B251" s="2" t="s">
+      <c r="B251" s="3" t="s">
         <v>1320</v>
       </c>
-      <c r="C251" s="2" t="s">
+      <c r="C251" s="3" t="s">
         <v>1321</v>
       </c>
-      <c r="D251" s="2" t="s">
+      <c r="D251" s="3" t="s">
         <v>1322</v>
       </c>
-      <c r="E251" s="2" t="s">
+      <c r="E251" s="3" t="s">
         <v>1323</v>
       </c>
-      <c r="F251" s="2" t="s">
+      <c r="F251" s="3" t="s">
         <v>1324</v>
       </c>
       <c r="G251" s="3" t="s">
@@ -10664,41 +10727,41 @@
     </row>
     <row r="252" customHeight="1" spans="1:7">
       <c r="A252" s="2"/>
-      <c r="B252" s="2" t="s">
+      <c r="B252" s="3" t="s">
         <v>1326</v>
       </c>
-      <c r="C252" s="2" t="s">
+      <c r="C252" s="3" t="s">
         <v>1327</v>
       </c>
-      <c r="D252" s="2" t="s">
+      <c r="D252" s="3" t="s">
         <v>1328</v>
       </c>
-      <c r="E252" s="2" t="s">
+      <c r="E252" s="3" t="s">
         <v>1329</v>
       </c>
-      <c r="F252" s="2" t="s">
+      <c r="F252" s="3" t="s">
         <v>1330</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="253" customHeight="1" spans="1:7">
       <c r="A253" s="2"/>
       <c r="B253" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>1332</v>
       </c>
-      <c r="C253" s="2" t="s">
+      <c r="D253" s="2" t="s">
         <v>1333</v>
       </c>
-      <c r="D253" s="2" t="s">
+      <c r="E253" s="2" t="s">
         <v>1334</v>
       </c>
-      <c r="E253" s="2" t="s">
+      <c r="F253" s="2" t="s">
         <v>1335</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>1336</v>
       </c>
       <c r="G253" s="3" t="s">
         <v>1336</v>
@@ -10722,129 +10785,129 @@
         <v>1341</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="255" customHeight="1" spans="1:7">
       <c r="A255" s="2"/>
       <c r="B255" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="C255" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="D255" s="2" t="s">
-        <v>253</v>
+        <v>1344</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>254</v>
+        <v>1345</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>255</v>
+        <v>1346</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>256</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="256" customHeight="1" spans="1:7">
       <c r="A256" s="2"/>
       <c r="B256" s="2" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="257" customHeight="1" spans="1:7">
       <c r="A257" s="2"/>
       <c r="B257" s="2" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="258" customHeight="1" spans="1:7">
       <c r="A258" s="2"/>
-      <c r="B258" s="3" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>1356</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>1357</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>1358</v>
-      </c>
-      <c r="F258" s="3" t="s">
+      <c r="B258" s="2" t="s">
         <v>1359</v>
       </c>
+      <c r="C258" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>1363</v>
+      </c>
       <c r="G258" s="3" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="259" customHeight="1" spans="1:7">
       <c r="A259" s="2"/>
-      <c r="B259" s="3" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C259" s="3" t="s">
-        <v>1362</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>1363</v>
-      </c>
-      <c r="E259" s="3" t="s">
-        <v>1363</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>1364</v>
+      <c r="B259" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>1365</v>
+        <v>256</v>
       </c>
     </row>
     <row r="260" customHeight="1" spans="1:7">
       <c r="A260" s="2"/>
-      <c r="B260" s="3" t="s">
+      <c r="B260" s="2" t="s">
         <v>1366</v>
       </c>
-      <c r="C260" s="3" t="s">
+      <c r="C260" s="2" t="s">
         <v>1367</v>
       </c>
-      <c r="D260" s="3" t="s">
+      <c r="D260" s="2" t="s">
         <v>1368</v>
       </c>
-      <c r="E260" s="3" t="s">
+      <c r="E260" s="2" t="s">
         <v>1369</v>
       </c>
-      <c r="F260" s="3" t="s">
+      <c r="F260" s="2" t="s">
         <v>1370</v>
       </c>
       <c r="G260" s="3" t="s">
@@ -10853,22 +10916,22 @@
     </row>
     <row r="261" customHeight="1" spans="1:7">
       <c r="A261" s="2"/>
-      <c r="B261" s="3" t="s">
+      <c r="B261" s="2" t="s">
         <v>1372</v>
       </c>
-      <c r="C261" s="3" t="s">
+      <c r="C261" s="2" t="s">
         <v>1373</v>
       </c>
-      <c r="D261" s="3" t="s">
+      <c r="D261" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="E261" s="6" t="s">
+      <c r="E261" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="F261" s="6" t="s">
+      <c r="F261" s="2" t="s">
         <v>1375</v>
       </c>
-      <c r="G261" s="6" t="s">
+      <c r="G261" s="3" t="s">
         <v>1376</v>
       </c>
     </row>
@@ -10905,202 +10968,202 @@
         <v>1385</v>
       </c>
       <c r="E263" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F263" s="3" t="s">
         <v>1386</v>
       </c>
-      <c r="F263" s="3" t="s">
+      <c r="G263" s="3" t="s">
         <v>1387</v>
-      </c>
-      <c r="G263" s="3" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="264" customHeight="1" spans="1:7">
       <c r="A264" s="2"/>
       <c r="B264" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C264" s="3" t="s">
         <v>1389</v>
       </c>
-      <c r="C264" s="3" t="s">
+      <c r="D264" s="3" t="s">
         <v>1390</v>
       </c>
-      <c r="D264" s="3" t="s">
+      <c r="E264" s="3" t="s">
         <v>1391</v>
       </c>
-      <c r="E264" s="3" t="s">
+      <c r="F264" s="3" t="s">
         <v>1392</v>
       </c>
-      <c r="F264" s="3" t="s">
+      <c r="G264" s="3" t="s">
         <v>1393</v>
-      </c>
-      <c r="G264" s="3" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="265" customHeight="1" spans="1:7">
       <c r="A265" s="2"/>
       <c r="B265" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C265" s="3" t="s">
         <v>1395</v>
       </c>
-      <c r="C265" s="3" t="s">
+      <c r="D265" s="3" t="s">
         <v>1396</v>
       </c>
-      <c r="D265" s="3" t="s">
+      <c r="E265" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F265" s="6" t="s">
         <v>1397</v>
       </c>
-      <c r="E265" s="3" t="s">
+      <c r="G265" s="6" t="s">
         <v>1398</v>
-      </c>
-      <c r="F265" s="3" t="s">
-        <v>1399</v>
-      </c>
-      <c r="G265" s="3" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="266" customHeight="1" spans="1:7">
       <c r="A266" s="2"/>
       <c r="B266" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D266" s="3" t="s">
         <v>1401</v>
       </c>
-      <c r="C266" s="3" t="s">
+      <c r="E266" s="3" t="s">
         <v>1402</v>
       </c>
-      <c r="D266" s="3" t="s">
+      <c r="F266" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="E266" s="3" t="s">
+      <c r="G266" s="3" t="s">
         <v>1404</v>
-      </c>
-      <c r="F266" s="3" t="s">
-        <v>1405</v>
-      </c>
-      <c r="G266" s="3" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="267" customHeight="1" spans="1:7">
       <c r="A267" s="2"/>
       <c r="B267" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D267" s="3" t="s">
         <v>1407</v>
       </c>
-      <c r="C267" s="3" t="s">
+      <c r="E267" s="3" t="s">
         <v>1408</v>
       </c>
-      <c r="D267" s="3" t="s">
+      <c r="F267" s="3" t="s">
         <v>1409</v>
       </c>
-      <c r="E267" s="3" t="s">
+      <c r="G267" s="3" t="s">
         <v>1410</v>
-      </c>
-      <c r="F267" s="3" t="s">
-        <v>1411</v>
-      </c>
-      <c r="G267" s="3" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="268" customHeight="1" spans="1:7">
       <c r="A268" s="2"/>
       <c r="B268" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D268" s="3" t="s">
         <v>1413</v>
       </c>
-      <c r="C268" s="3" t="s">
+      <c r="E268" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="D268" s="3" t="s">
+      <c r="F268" s="3" t="s">
         <v>1415</v>
       </c>
-      <c r="E268" s="3" t="s">
+      <c r="G268" s="3" t="s">
         <v>1416</v>
-      </c>
-      <c r="F268" s="3" t="s">
-        <v>1417</v>
-      </c>
-      <c r="G268" s="3" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="269" customHeight="1" spans="1:7">
       <c r="A269" s="2"/>
       <c r="B269" s="3" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D269" s="3" t="s">
         <v>1419</v>
       </c>
-      <c r="C269" s="3" t="s">
+      <c r="E269" s="3" t="s">
         <v>1420</v>
       </c>
-      <c r="D269" s="3" t="s">
+      <c r="F269" s="3" t="s">
         <v>1421</v>
       </c>
-      <c r="E269" s="3" t="s">
+      <c r="G269" s="3" t="s">
         <v>1422</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G269" s="3" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="270" customHeight="1" spans="1:7">
       <c r="A270" s="2"/>
       <c r="B270" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D270" s="3" t="s">
         <v>1425</v>
       </c>
-      <c r="C270" s="3" t="s">
+      <c r="E270" s="3" t="s">
         <v>1426</v>
       </c>
-      <c r="D270" s="3" t="s">
+      <c r="F270" s="3" t="s">
         <v>1427</v>
       </c>
-      <c r="E270" s="3" t="s">
+      <c r="G270" s="3" t="s">
         <v>1428</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>1429</v>
-      </c>
-      <c r="G270" s="3" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="271" customHeight="1" spans="1:7">
       <c r="A271" s="2"/>
       <c r="B271" s="3" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D271" s="3" t="s">
         <v>1431</v>
       </c>
-      <c r="C271" s="3" t="s">
+      <c r="E271" s="3" t="s">
         <v>1432</v>
       </c>
-      <c r="D271" s="3" t="s">
+      <c r="F271" s="3" t="s">
         <v>1433</v>
       </c>
-      <c r="E271" s="3" t="s">
+      <c r="G271" s="3" t="s">
         <v>1434</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>1435</v>
-      </c>
-      <c r="G271" s="3" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="272" customHeight="1" spans="1:7">
       <c r="A272" s="2"/>
       <c r="B272" s="3" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D272" s="3" t="s">
         <v>1437</v>
       </c>
-      <c r="C272" s="3" t="s">
+      <c r="E272" s="3" t="s">
         <v>1438</v>
       </c>
-      <c r="D272" s="3" t="s">
+      <c r="F272" s="3" t="s">
         <v>1439</v>
       </c>
-      <c r="E272" s="6" t="s">
+      <c r="G272" s="3" t="s">
         <v>1440</v>
-      </c>
-      <c r="F272" s="6" t="s">
-        <v>1438</v>
-      </c>
-      <c r="G272" s="6" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="273" customHeight="1" spans="1:7">
@@ -11157,13 +11220,13 @@
         <v>1455</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1457</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="276" customHeight="1" spans="1:7">
@@ -11177,56 +11240,140 @@
       <c r="D276" s="3" t="s">
         <v>1460</v>
       </c>
-      <c r="E276" s="3" t="s">
+      <c r="E276" s="6" t="s">
         <v>1461</v>
       </c>
-      <c r="F276" s="3" t="s">
-        <v>1462</v>
-      </c>
-      <c r="G276" s="3" t="s">
-        <v>1463</v>
+      <c r="F276" s="6" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G276" s="6" t="s">
+        <v>1459</v>
       </c>
     </row>
     <row r="277" customHeight="1" spans="1:7">
       <c r="A277" s="2"/>
       <c r="B277" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D277" s="3" t="s">
         <v>1464</v>
       </c>
-      <c r="C277" s="3" t="s">
+      <c r="E277" s="3" t="s">
         <v>1465</v>
       </c>
-      <c r="D277" s="3" t="s">
+      <c r="F277" s="3" t="s">
         <v>1466</v>
       </c>
-      <c r="E277" s="3" t="s">
+      <c r="G277" s="3" t="s">
         <v>1467</v>
-      </c>
-      <c r="F277" s="3" t="s">
-        <v>1468</v>
-      </c>
-      <c r="G277" s="3" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="278" customHeight="1" spans="1:7">
       <c r="A278" s="2"/>
       <c r="B278" s="3" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D278" s="3" t="s">
         <v>1470</v>
       </c>
-      <c r="C278" s="3" t="s">
+      <c r="E278" s="3" t="s">
         <v>1471</v>
       </c>
-      <c r="D278" s="3" t="s">
+      <c r="F278" s="3" t="s">
         <v>1472</v>
       </c>
-      <c r="E278" s="6" t="s">
+      <c r="G278" s="3" t="s">
         <v>1473</v>
       </c>
-      <c r="F278" s="6" t="s">
+    </row>
+    <row r="279" customHeight="1" spans="1:7">
+      <c r="A279" s="2"/>
+      <c r="B279" s="3" t="s">
         <v>1474</v>
       </c>
-      <c r="G278" s="6" t="s">
+      <c r="C279" s="3" t="s">
         <v>1475</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="280" customHeight="1" spans="1:7">
+      <c r="A280" s="2"/>
+      <c r="B280" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="281" customHeight="1" spans="1:7">
+      <c r="A281" s="2"/>
+      <c r="B281" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="282" customHeight="1" spans="1:7">
+      <c r="A282" s="2"/>
+      <c r="B282" s="3" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F282" s="6" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G282" s="6" t="s">
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -11234,15 +11381,15 @@
     <mergeCell ref="A3:A18"/>
     <mergeCell ref="A19:A35"/>
     <mergeCell ref="A36:A68"/>
-    <mergeCell ref="A69:A78"/>
-    <mergeCell ref="A79:A91"/>
-    <mergeCell ref="A92:A96"/>
-    <mergeCell ref="A97:A107"/>
-    <mergeCell ref="A108:A127"/>
-    <mergeCell ref="A128:A137"/>
-    <mergeCell ref="A138:A197"/>
-    <mergeCell ref="A198:A210"/>
-    <mergeCell ref="A211:A278"/>
+    <mergeCell ref="A69:A79"/>
+    <mergeCell ref="A80:A92"/>
+    <mergeCell ref="A93:A97"/>
+    <mergeCell ref="A98:A108"/>
+    <mergeCell ref="A109:A128"/>
+    <mergeCell ref="A129:A138"/>
+    <mergeCell ref="A139:A198"/>
+    <mergeCell ref="A199:A211"/>
+    <mergeCell ref="A212:A282"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
